--- a/docs/데이터_계보_등록부.xlsx
+++ b/docs/데이터_계보_등록부.xlsx
@@ -9,12 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="표지" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="원천 데이터 등록부" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM 파생 분석 산출물" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="용어 설명" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="헤더 매핑 상세" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM 파생 분석 산출물" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="용어 설명" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'원천 데이터 등록부'!$A$1:$O$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'LLM 파생 분석 산출물'!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'LLM 파생 분석 산출물'!$A$1:$J$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,8 +79,20 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +107,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F0FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEBD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAECEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,6 +208,28 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -572,7 +627,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -584,7 +639,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>어학(language_qualification), 근무 경력(work_experience) — 2026-08-29 신규 추가 데이터 반영</t>
+          <t>직무_직군_맵핑(mapping_job_function), 직군 예외자(exception_job_function), 평가표기 예외자(evaluation_exception) 3개 원천 추가 반영 + "헤더 매핑 상세" 시트 신설(원본 헤더 → 처리 컬럼 전체 매핑) + 근무 경력 누적 방식 정정(그룹 교체 → 자연키 upsert, 2026-09-02 변경 반영) + 팀/리더 참조 웹 업로드 지원 방식 갱신(2026-09-11)</t>
         </is>
       </c>
     </row>
@@ -649,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2232,7 +2287,7 @@
       <c r="H22" s="9" t="inlineStr">
         <is>
           <t>날짜 기반 누적
-(dep_id별 최신 스냅샷)</t>
+(dep_id별 최신 스냅샷, dep_id는 1/2/3단계부서명 경로에서 자동 계산 — 이름이 바뀌어도 재계산됨)</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -2248,7 +2303,8 @@
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>지원 (exact, 기준 연/월 지정 + 백필)</t>
+          <t>지원 (wildcard: xlsx 또는 csv, 기준 연/월/일 지정 + 대량 백필)
+※ 2026-09-11부터 인텔이크 스키마가 1/2/3단계부서명 "전체 경로 포함" 형태로 변경되고 dep_id/upper_dep_id/team_layer는 자동 계산됨</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -2381,14 +2437,14 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>그룹 교체
-(researcher_id 단위 —
-한 사람 경력 전체를 매번 교체)</t>
+          <t>자연키 upsert
+(researcher_id + company_name + work_start_date)
+※ 2026-09-02부터 그룹 교체(researcher_id 단위 전체 교체)에서 자연키 upsert로 전환 — 본인 경력은 소급 수정이 거의 없고, 전배·퇴직으로 이번 업로드에 없는 사람의 기존 경력도 보존하기 위함</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>researcher_id (그룹키)</t>
+          <t>researcher_id + company_name + work_start_date</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
@@ -2418,7 +2474,7 @@
       </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>2026-08-29 신규 추가</t>
+          <t>2026-08-29 신규 추가 (2026-09-02: 누적 방식을 그룹 교체→자연키 upsert로 변경)</t>
         </is>
       </c>
     </row>
@@ -2718,11 +2774,241 @@
       </c>
       <c r="O28" s="9" t="inlineStr"/>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>※ 노란색 강조 행 = 2026-08-29 신규 추가(어학, 근무 경력)</t>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>원천 정제(전용 처리기 있음)</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>직무_직군_맵핑</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>mapping_job_function.csv</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>직무_직군_맵핑.xlsx</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>1번째 행</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>process_mapping_job_function.py</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>전체 교체
+(누적 안 함 — researcher_id 없는 순수 참조 테이블)</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>- (자연키 없음, job_function이 사실상 조회키)</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>지원 (exact)</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M29" s="11" t="inlineStr">
+        <is>
+          <t>미노출
+(화이트리스트 없음)</t>
+        </is>
+      </c>
+      <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>연구원 프로필 "보유기술" DS/SAIT직군 배지, 전문성 MAP 호버 라벨 (services/job_category.py가 researchers.csv의 job_function과 텍스트 매칭)</t>
+        </is>
+      </c>
+      <c r="O29" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-04 신규 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>원천 정제(전용 처리기 있음)</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>직군 예외자</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>exception_job_function.csv</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>직무_직군_맵핑_예외자.xlsx</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>1번째 행</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>process_exception_job_function.py</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>전체 교체
+(누적 안 함 — 시점 개념 없는 현재값 테이블)</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="11" t="inlineStr">
+        <is>
+          <t>지원 (exact) + 관리자 화면 그리드 CRUD 병행
+(services/exception_job_function_store.py)</t>
+        </is>
+      </c>
+      <c r="L30" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>미노출
+(화이트리스트 없음)</t>
+        </is>
+      </c>
+      <c r="N30" s="11" t="inlineStr">
+        <is>
+          <t>mapping_job_function 매칭 결과와 무관하게 researcher_id 기준으로 SAIT직군 값을 강제 override(DS는 그대로 유지) — 연구원 프로필·전문성 MAP 동일 반영</t>
+        </is>
+      </c>
+      <c r="O30" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-09 신규 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>원천 정제(전용 처리기 있음)</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>평가표기 예외자</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>evaluation_exception.csv</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>평가표기예외자.xlsx</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>1번째 행</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>process_evaluation_exception.py</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>전체 교체
+(누적 안 함 — 시점 개념 없는 현재값 테이블)</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>지원 (exact)</t>
+        </is>
+      </c>
+      <c r="L31" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
+          <t>노출(view_evaluation 권한 필요)</t>
+        </is>
+      </c>
+      <c r="N31" s="11" t="inlineStr">
+        <is>
+          <t>T&amp;P 평가 표기 3분기 로직(연봉등급 있음/없음/예외자)에서 예외자 명단이면 연봉등급 없이도 하반기업적만 표시 — 화면·A4 인쇄카드·엑셀 다운로드 공통 반영</t>
+        </is>
+      </c>
+      <c r="O31" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-09 신규 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>※ 노란색 강조 행 = 2026-09-18 신규 추가(직무_직군_맵핑, 직군 예외자, 평가표기 예외자)</t>
         </is>
       </c>
     </row>
@@ -2738,7 +3024,7140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G319"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>데이터명</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>처리 스크립트
+(pipeline/)</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="E1" s="17" t="inlineStr">
+        <is>
+          <t>원본 헤더</t>
+        </is>
+      </c>
+      <c r="F1" s="17" t="inlineStr">
+        <is>
+          <t>출력 컬럼</t>
+        </is>
+      </c>
+      <c r="G1" s="17" t="inlineStr">
+        <is>
+          <t>처리 설명(변환 로직 / 필터·정렬·병합 규칙)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>인력현황</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>process_researchers.py</t>
+        </is>
+      </c>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>사원번호</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>norm_id() 8자리 zero-pad; 빈 값이면 행 제거. 필수 컬럼(없으면 중단).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>trim만. 필수 컬럼(없으면 중단).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>현소속부서명</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>비공식소속부서명</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>org_code</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>trim만 — team_refer.csv의 org_name_wd와 매칭되는 핵심 키.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>trim 후 POSITION_LABEL_MAP으로 영문 임원 표기만 한글 치환('Corporate VP'→'상무' 등), CL1~CL6 등은 원본 그대로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>직무</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>job_function</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>trim만 — mapping_job_function.csv/exception_job_function.csv와 텍스트 매칭되는 키.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>4직종</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>job_type</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>국적</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>nationality</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>법적생년월일성별</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>birth_year, birth_date</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>_parse_birth_date(): 앞 6자리를 YYMMDD로 해석(yy&gt;=26→1900+yy, else 2000+yy); 달력상 유효하지 않으면 둘 다 공란.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>근속 기준일_그룹입사일</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>hire_date</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>_parse_date(): %Y-%m-%d/%Y/%m/%d/%Y.%m.%d/%Y%m%d 순으로 시도 → YYYY-MM-DD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>승격산정기준일자</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>promotion_date</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>hire_date와 동일한 _parse_date() 로직.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Knox ID</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>knox_id</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>trim만 — 리더십진단(process_leadership.py)이 Knox ID→researcher_id 조회에 사용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>재직상태명</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>employment_status</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>trim만, 원본 표기 그대로(휴직/재직/퇴직 등).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>인원실적년도</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>valid_year</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>숫자만 추출해 앞 4자리(4자리 미만이면 공란).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>인원실적월</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>valid_month</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>숫자만 추출해 2자리 zero-pad(1~12 범위 밖이면 공란).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>is_current</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>병합 후 전체 파일에서 (valid_year,valid_month) 최댓값을 구해, 그 값과 같은 행만 'Y' 나머지 'N'(시점 정보 자체가 없는 행은 항상 'Y'). 매 실행마다 전체 재계산.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>age/tenure/position_year</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>docstring에 계산 언급은 있으나 실제로는 CSV에 저장하지 않음(표시 전용, 화면에서 그때그때 계산).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr"/>
+      <c r="F21" s="9" t="inlineStr"/>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id 빈 행 제거. 사원번호/성명 없으면 전체 중단. researcher_id+valid_year+valid_month 오름차순 정렬 후 병합(동일 사람 여러 시점이면 최신이 마지막).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr"/>
+      <c r="F22" s="9" t="inlineStr"/>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>researchers.csv: researcher_id 키로 업서트(이번 파일에 없는 사람은 이전 행 보존, 삭제 안 함). researchers_history.csv: (researcher_id,valid_year,valid_month) 키로 append(모든 월별 스냅샷 누적, 건너뛴 것도 포함).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>T&amp;P(평가)</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>process_tp_evaluation.py</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id(내부 _rid)</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>norm_id() 8자리 zero-pad; 빈 값 제거. 필수(없으면 ValueError).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>컬럼이 존재할 때만 추출, trim만 — researchers.csv 보정용 별도 반환값(researcher_updates).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>컬럼 존재 시만, trim만 — 위와 동일 용도.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>생년월일</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>birth_year</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>_parse_birth_year(): 앞 4자리가 숫자이고 1900&lt;year&lt;=2010이면 채택, 아니면 pd.to_datetime()의 .year, 그것도 실패하면 공란.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>'{연도} 연봉등급' (동적, 회계연도 3개년)</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>salary_grade_column(year) (예: 2024_salary_grade)</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>값은 strip 후 SALARY_GRADES(가/나/다/라/마) 화이트리스트 검증 — 밖의 값/공란은 공란 처리 + WARN 카운트. 회계연도 3개년은 services.evaluations.evaluation_years(valid_date) 계산.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="8" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>'{연도} 상반기업적' (동적, 연봉등급 3개년보다 1년 전 3개년)</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>first_half_column(year)</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>strip('nan'→'')만, 값 제한 없음(2026-08-29부터 EM/ES/MT 등 원본값 그대로 허용).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>'{연도} 하반기업적' (동적)</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>second_half_column(year)</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>상반기업적과 동일하게 값 제한 없이 strip만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>valid_year, valid_month</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>원본 컬럼이 아니라 process() 호출 시점의 valid_date 인자(기본 오늘)에서 직접 계산.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>(컬럼명 자체가 계산값)</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>salary_grade_column/first_half_column/second_half_column</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>출력 컬럼 '이름' 자체가 매번 회계연도 산술로 계산되는 템플릿(고정 1:1 매핑이 아님) — services/evaluations.py의 current_fiscal_year()(3월 시작) 기준.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="8" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr"/>
+      <c r="F33" s="9" t="inlineStr"/>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-09부터 '역량'(competency) 컬럼은 완전히 제외(더 이상 읽지 않음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr"/>
+      <c r="F34" s="9" t="inlineStr"/>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>사번 빈 행 제거, 없으면 전체 중단. 연봉등급/반기 컬럼이 하나도 안 잡히면 evaluations.csv 저장 자체를 건너뜀(이름/성별/생년월일 갱신은 별도로 계속 반환).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="8" t="n"/>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr"/>
+      <c r="F35" s="9" t="inlineStr"/>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>write_merged_with_valid_period(): 기존 저장된 시점보다 이번 valid_date가 과거면 그 사람 행은 건너뜀(경고), evaluations_history.csv에는 건너뛴 것 포함 항상 append.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>특허</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>process_patents.py</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="n"/>
+      <c r="E36" s="19" t="n"/>
+      <c r="F36" s="19" t="n"/>
+      <c r="G36" s="19" t="n"/>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="8" t="n"/>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>norm_id() 8자리; 빈 값 제거. 필수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>접수ID</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>application_id</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>trim만. 필수 — 자연키의 일부.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="8" t="n"/>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>발명명칭 - 영문</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>발명명칭</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>title_ko</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="45" customHeight="1">
+      <c r="A41" s="8" t="n"/>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>지분율</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>share_ratio</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="45" customHeight="1">
+      <c r="A42" s="8" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>대표발명자여부</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>is_lead_inventor</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="45" customHeight="1">
+      <c r="A43" s="8" t="n"/>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>현재등급</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>patent_grade</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="45" customHeight="1">
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>현재등급 - A급구분</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>patent_grade_a_sub</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="45" customHeight="1">
+      <c r="A45" s="8" t="n"/>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>출원번호</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>application_no</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>trim만(선택 컬럼, 없으면 공란).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="45" customHeight="1">
+      <c r="A46" s="8" t="n"/>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>출원일 (없으면 출원일자)</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>application_date</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>parse_yyyymmdd() → YYYY-MM-DD. 두 이름 중 먼저 발견되는 것만 사용, 둘 다 없으면 공란.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="45" customHeight="1">
+      <c r="A47" s="8" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>등록번호</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>registration_no</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>trim만(선택).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="45" customHeight="1">
+      <c r="A48" s="8" t="n"/>
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>등록일 (없으면 등록일자)</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>registration_date</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>parse_yyyymmdd(), application_date와 동일한 fallback.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" s="8" t="n"/>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>국가 (없으면 국가명)</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="45" customHeight="1">
+      <c r="A50" s="8" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>과제명</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>project_name</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>trim만(선택, 타임라인 특허↔과제 연결용).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1">
+      <c r="A51" s="8" t="n"/>
+      <c r="B51" s="9" t="n"/>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>과제코드</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>project_code</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>trim만(선택, 동일 용도).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="45" customHeight="1">
+      <c r="A52" s="8" t="n"/>
+      <c r="B52" s="9" t="n"/>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>(없음 — 진행상태 컬럼은 무시)</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>원본 '진행상태' 컬럼은 전혀 안 읽음. application_no 있으면 '출원', registration_no까지 있으면 '등록'(등록 우선), 둘 다 없으면 공란 — 존재 여부만으로 재계산.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="45" customHeight="1">
+      <c r="A53" s="8" t="n"/>
+      <c r="B53" s="9" t="n"/>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr"/>
+      <c r="F53" s="9" t="inlineStr"/>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id 빈 행 제거. 사번/접수ID 필수(없으면 중단).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="45" customHeight="1">
+      <c r="A54" s="8" t="n"/>
+      <c r="B54" s="9" t="n"/>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr"/>
+      <c r="F54" s="9" t="inlineStr"/>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>발명자별 1행 유지 원칙(같은 접수ID=같은 특허, 발명자 수만큼 행) — inventor 단위 dedup 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="45" customHeight="1">
+      <c r="A55" s="8" t="n"/>
+      <c r="B55" s="9" t="n"/>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr"/>
+      <c r="F55" s="9" t="inlineStr"/>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id, application_id 순 정렬. write_merged()(시점보호 없음)로 TABLE_KEYS['patents'] 키 upsert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>양성이력</t>
+        </is>
+      </c>
+      <c r="C56" s="19" t="inlineStr">
+        <is>
+          <t>process_nurturing.py</t>
+        </is>
+      </c>
+      <c r="D56" s="19" t="n"/>
+      <c r="E56" s="19" t="n"/>
+      <c r="F56" s="19" t="n"/>
+      <c r="G56" s="19" t="n"/>
+    </row>
+    <row r="57" ht="45" customHeight="1">
+      <c r="A57" s="8" t="n"/>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>norm_id(); 빈 값 제거. 필수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="45" customHeight="1">
+      <c r="A58" s="8" t="n"/>
+      <c r="B58" s="9" t="n"/>
+      <c r="C58" s="9" t="n"/>
+      <c r="D58" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>양성구분</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
+      <c r="A59" s="8" t="n"/>
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>세부양성구분</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>subcategory</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="A60" s="8" t="n"/>
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>연수시작일</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>parse_flexible_date() → YYYY-MM-DD(다양한 포맷 + '9999-12-31' 같은 sentinel 날짜 정규식 폴백 지원). 컬럼 없으면 공란.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="45" customHeight="1">
+      <c r="A61" s="8" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>연수종료일</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>start_date와 동일.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="45" customHeight="1">
+      <c r="A62" s="8" t="n"/>
+      <c r="B62" s="9" t="n"/>
+      <c r="C62" s="9" t="n"/>
+      <c r="D62" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>국가</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="45" customHeight="1">
+      <c r="A63" s="8" t="n"/>
+      <c r="B63" s="9" t="n"/>
+      <c r="C63" s="9" t="n"/>
+      <c r="D63" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>도시</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="45" customHeight="1">
+      <c r="A64" s="8" t="n"/>
+      <c r="B64" s="9" t="n"/>
+      <c r="C64" s="9" t="n"/>
+      <c r="D64" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>교육기관</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>institution</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="45" customHeight="1">
+      <c r="A65" s="8" t="n"/>
+      <c r="B65" s="9" t="n"/>
+      <c r="C65" s="9" t="n"/>
+      <c r="D65" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>전공학과</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="45" customHeight="1">
+      <c r="A66" s="8" t="n"/>
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="9" t="n"/>
+      <c r="D66" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>의무근무 종료일</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>service_end_date</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>parse_flexible_date() — '9999-12-31'(무기한) sentinel이 실제로 나오는 대표 필드.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="45" customHeight="1">
+      <c r="A67" s="8" t="n"/>
+      <c r="B67" s="9" t="n"/>
+      <c r="C67" s="9" t="n"/>
+      <c r="D67" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>start_date 결과의 앞 4자리 문자열로 파생(빈 값이면 NA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="45" customHeight="1">
+      <c r="A68" s="8" t="n"/>
+      <c r="B68" s="9" t="n"/>
+      <c r="C68" s="9" t="n"/>
+      <c r="D68" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr"/>
+      <c r="F68" s="9" t="inlineStr"/>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>사번 빈 행 제거, 없으면 중단. researcher_id, start_date 순 정렬. write_merged()(시점보호 없음) TABLE_KEYS['nurturing'] upsert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>시상이력</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="inlineStr">
+        <is>
+          <t>process_awards.py</t>
+        </is>
+      </c>
+      <c r="D69" s="19" t="n"/>
+      <c r="E69" s="19" t="n"/>
+      <c r="F69" s="19" t="n"/>
+      <c r="G69" s="19" t="n"/>
+    </row>
+    <row r="70" ht="45" customHeight="1">
+      <c r="A70" s="8" t="n"/>
+      <c r="B70" s="9" t="n"/>
+      <c r="C70" s="9" t="n"/>
+      <c r="D70" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>norm_id(); 빈 값 제거. 필수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="45" customHeight="1">
+      <c r="A71" s="8" t="n"/>
+      <c r="B71" s="9" t="n"/>
+      <c r="C71" s="9" t="n"/>
+      <c r="D71" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>수상일</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>award_date</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>parse_flexible_date() → YYYY-MM-DD. 컬럼 없으면 공란.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="45" customHeight="1">
+      <c r="A72" s="8" t="n"/>
+      <c r="B72" s="9" t="n"/>
+      <c r="C72" s="9" t="n"/>
+      <c r="D72" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>수상 유형</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>award_type</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="45" customHeight="1">
+      <c r="A73" s="8" t="n"/>
+      <c r="B73" s="9" t="n"/>
+      <c r="C73" s="9" t="n"/>
+      <c r="D73" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>수상명</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>award_name</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="45" customHeight="1">
+      <c r="A74" s="8" t="n"/>
+      <c r="B74" s="9" t="n"/>
+      <c r="C74" s="9" t="n"/>
+      <c r="D74" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>수여기관</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>awarding_org</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="45" customHeight="1">
+      <c r="A75" s="8" t="n"/>
+      <c r="B75" s="9" t="n"/>
+      <c r="C75" s="9" t="n"/>
+      <c r="D75" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="45" customHeight="1">
+      <c r="A76" s="8" t="n"/>
+      <c r="B76" s="9" t="n"/>
+      <c r="C76" s="9" t="n"/>
+      <c r="D76" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>award_date 앞 4자리로 파생(빈 값이면 NA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="45" customHeight="1">
+      <c r="A77" s="8" t="n"/>
+      <c r="B77" s="9" t="n"/>
+      <c r="C77" s="9" t="n"/>
+      <c r="D77" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr"/>
+      <c r="F77" s="9" t="inlineStr"/>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>사번 빈 행 제거, 없으면 중단. researcher_id 오름차순 + award_date 내림차순(최근 수상이 먼저) 정렬. write_merged() TABLE_KEYS['awards'] upsert(시점보호 없음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B78" s="19" t="inlineStr">
+        <is>
+          <t>학력</t>
+        </is>
+      </c>
+      <c r="C78" s="19" t="inlineStr">
+        <is>
+          <t>process_education.py</t>
+        </is>
+      </c>
+      <c r="D78" s="19" t="n"/>
+      <c r="E78" s="19" t="n"/>
+      <c r="F78" s="19" t="n"/>
+      <c r="G78" s="19" t="n"/>
+    </row>
+    <row r="79" ht="45" customHeight="1">
+      <c r="A79" s="8" t="n"/>
+      <c r="B79" s="9" t="n"/>
+      <c r="C79" s="9" t="n"/>
+      <c r="D79" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>norm_id(); 빈 값 제거.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="45" customHeight="1">
+      <c r="A80" s="8" t="n"/>
+      <c r="B80" s="9" t="n"/>
+      <c r="C80" s="9" t="n"/>
+      <c r="D80" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>학력</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>_normalize_degree(): trim+소문자화 후 키워드 매칭으로 박사/석사/학사/전문대/고교 5개 표준값 중 하나로 통일. 표준 어디에도 안 맞으면 원본(trim만) 그대로 보존.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="45" customHeight="1">
+      <c r="A81" s="8" t="n"/>
+      <c r="B81" s="9" t="n"/>
+      <c r="C81" s="9" t="n"/>
+      <c r="D81" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>학교명</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>trim + clean_str(); 컬럼 없으면 공란.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="45" customHeight="1">
+      <c r="A82" s="8" t="n"/>
+      <c r="B82" s="9" t="n"/>
+      <c r="C82" s="9" t="n"/>
+      <c r="D82" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>전공</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>trim + clean_str(); 컬럼 없으면 공란.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="45" customHeight="1">
+      <c r="A83" s="8" t="n"/>
+      <c r="B83" s="9" t="n"/>
+      <c r="C83" s="9" t="n"/>
+      <c r="D83" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>학위 취득 연도</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>graduation_year (1순위)</t>
+        </is>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>정수/실수문자열→int, 1900~2100 범위면 채택.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="45" customHeight="1">
+      <c r="A84" s="8" t="n"/>
+      <c r="B84" s="9" t="n"/>
+      <c r="C84" s="9" t="n"/>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>졸업일</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>graduation_year (fallback)</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>학위 취득 연도가 없거나 범위 밖이면 pd.to_datetime()으로 연도만 추출해 대체.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="45" customHeight="1">
+      <c r="A85" s="8" t="n"/>
+      <c r="B85" s="9" t="n"/>
+      <c r="C85" s="9" t="n"/>
+      <c r="D85" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr"/>
+      <c r="F85" s="9" t="inlineStr"/>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id 빈 행 제거.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="45" customHeight="1">
+      <c r="A86" s="8" t="n"/>
+      <c r="B86" s="9" t="n"/>
+      <c r="C86" s="9" t="n"/>
+      <c r="D86" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr"/>
+      <c r="F86" s="9" t="inlineStr"/>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>연구원별 '최종학력'(DEG_ORDER 우선순위: 박사&gt;석사&gt;학사&gt;전문대&gt;고교) 판정 후 _KEEP_MAP에 정의된 하위 학력 행만 보존(예: 최종학력=학사 → 학사/전문대/고교만 남기고 나머지 표준학위 행 제거). 5개 표준 밖 원본 표기(예: '수료')는 이 필터 대상이 아니라 항상 보존. 표준 학위가 하나도 없으면 전부 통과. (2026-09-09 정정: 예전엔 '학사 이상 있으면 전문대/고교 삭제'라는 더 거친 규칙이었음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="45" customHeight="1">
+      <c r="A87" s="8" t="n"/>
+      <c r="B87" s="9" t="n"/>
+      <c r="C87" s="9" t="n"/>
+      <c r="D87" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr"/>
+      <c r="F87" s="9" t="inlineStr"/>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id, 학위 우선순위 순 정렬 후 write_merged() TABLE_KEYS['education'] upsert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B88" s="19" t="inlineStr">
+        <is>
+          <t>리더십진단</t>
+        </is>
+      </c>
+      <c r="C88" s="19" t="inlineStr">
+        <is>
+          <t>process_leadership.py</t>
+        </is>
+      </c>
+      <c r="D88" s="19" t="n"/>
+      <c r="E88" s="19" t="n"/>
+      <c r="F88" s="19" t="n"/>
+      <c r="G88" s="19" t="n"/>
+    </row>
+    <row r="89" ht="45" customHeight="1">
+      <c r="A89" s="8" t="n"/>
+      <c r="B89" s="9" t="n"/>
+      <c r="C89" s="9" t="n"/>
+      <c r="D89" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>진단대상자ID</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>사번이 아니라 Knox ID — researchers.csv의 knox_id 컬럼과 대소문자 무관 매칭해 researcher_id로 역조회. 매칭 실패하면 researcher_id=''로 그 행 제거(최대 20건 WARN 나열). researchers.csv가 없거나 knox_id/researcher_id 컬럼이 없으면 전체 중단. 전원 매칭 실패면 이번 파일 전체를 SKIP(기존 파일 보존).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="45" customHeight="1">
+      <c r="A90" s="8" t="n"/>
+      <c r="B90" s="9" t="n"/>
+      <c r="C90" s="9" t="n"/>
+      <c r="D90" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>평가자그룹명</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>evaluator_group</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>trim만(본인/동료/상사/부서원).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="45" customHeight="1">
+      <c r="A91" s="8" t="n"/>
+      <c r="B91" s="9" t="n"/>
+      <c r="C91" s="9" t="n"/>
+      <c r="D91" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>문항 1,2,3,4</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>미래통찰</t>
+        </is>
+      </c>
+      <c r="G91" s="9" t="inlineStr">
+        <is>
+          <t>쉼표→점 치환 후 숫자화, 동일 (researcher_id,year,evaluator_group) 내 평균 → 4문항 평균 → 소수 2자리 반올림.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="45" customHeight="1">
+      <c r="A92" s="8" t="n"/>
+      <c r="B92" s="9" t="n"/>
+      <c r="C92" s="9" t="n"/>
+      <c r="D92" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>문항 5,6,7,8</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>성과창출</t>
+        </is>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
+        <is>
+          <t>미래통찰과 동일한 2단계 평균 방식.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="45" customHeight="1">
+      <c r="A93" s="8" t="n"/>
+      <c r="B93" s="9" t="n"/>
+      <c r="C93" s="9" t="n"/>
+      <c r="D93" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>문항 9,10,11,12</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>몰입촉진</t>
+        </is>
+      </c>
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>동일.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="45" customHeight="1">
+      <c r="A94" s="8" t="n"/>
+      <c r="B94" s="9" t="n"/>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>문항 13,14,15,16</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>인재육성</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>동일.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="45" customHeight="1">
+      <c r="A95" s="8" t="n"/>
+      <c r="B95" s="9" t="n"/>
+      <c r="C95" s="9" t="n"/>
+      <c r="D95" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>문항 17,18,19,20</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>자기관리</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>동일.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="45" customHeight="1">
+      <c r="A96" s="8" t="n"/>
+      <c r="B96" s="9" t="n"/>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>문항 21~26</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>저해행동</t>
+        </is>
+      </c>
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>동일(6문항 평균).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="45" customHeight="1">
+      <c r="A97" s="8" t="n"/>
+      <c r="B97" s="9" t="n"/>
+      <c r="C97" s="9" t="n"/>
+      <c r="D97" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>문항 27,28</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>(미매핑)</t>
+        </is>
+      </c>
+      <c r="G97" s="9" t="inlineStr">
+        <is>
+          <t>df에는 읽히지만 6개 역량군 어디에도 속하지 않아 출력 컬럼으로 안 나감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="45" customHeight="1">
+      <c r="A98" s="8" t="n"/>
+      <c r="B98" s="9" t="n"/>
+      <c r="C98" s="9" t="n"/>
+      <c r="D98" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>강점</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>strengths (leadership_comments.csv)</t>
+        </is>
+      </c>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>trim + clean_str().</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="45" customHeight="1">
+      <c r="A99" s="8" t="n"/>
+      <c r="B99" s="9" t="n"/>
+      <c r="C99" s="9" t="n"/>
+      <c r="D99" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>개선점</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>improvements (leadership_comments.csv)</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>trim + clean_str().</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="45" customHeight="1">
+      <c r="A100" s="8" t="n"/>
+      <c r="B100" s="9" t="n"/>
+      <c r="C100" s="9" t="n"/>
+      <c r="D100" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>(없음, COL_YEAR 설정이 공백)</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>소스 헤더에서 읽지 않음 — 실행 시점의 datetime.now().year를 모든 행에 일괄 적용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="45" customHeight="1">
+      <c r="A101" s="8" t="n"/>
+      <c r="B101" s="9" t="n"/>
+      <c r="C101" s="9" t="n"/>
+      <c r="D101" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>(28문항 부분집합의 평균)</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>미래통찰~저해행동 6개 역량 점수</t>
+        </is>
+      </c>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>위 매핑 참고 — 2단계 평균(평가자 내 평균 → 문항군 평균).</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="45" customHeight="1">
+      <c r="A102" s="8" t="n"/>
+      <c r="B102" s="9" t="n"/>
+      <c r="C102" s="9" t="n"/>
+      <c r="D102" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>(합성 행)</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>evaluator_group='타인평균'</t>
+        </is>
+      </c>
+      <c r="G102" s="9" t="inlineStr">
+        <is>
+          <t>원본 행이 아니라 동료+상사+부서원 3개 그룹 점수의 평균으로 새로 생성된 행(연구원×연도 단위 추가).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="45" customHeight="1">
+      <c r="A103" s="8" t="n"/>
+      <c r="B103" s="9" t="n"/>
+      <c r="C103" s="9" t="n"/>
+      <c r="D103" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>(문자열 조합)</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>commenter_type (leadership_comments.csv)</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="inlineStr">
+        <is>
+          <t>f'리더십_{평가자그룹명}' 형태로 조합.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="45" customHeight="1">
+      <c r="A104" s="8" t="n"/>
+      <c r="B104" s="9" t="n"/>
+      <c r="C104" s="9" t="n"/>
+      <c r="D104" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>(하드코딩)</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>comment_raw, comment_summary (leadership_comments.csv)</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr">
+        <is>
+          <t>항상 빈 문자열로 채움(이 소스 전용).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="45" customHeight="1">
+      <c r="A105" s="8" t="n"/>
+      <c r="B105" s="9" t="n"/>
+      <c r="C105" s="9" t="n"/>
+      <c r="D105" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr"/>
+      <c r="F105" s="9" t="inlineStr"/>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>Knox ID 매칭 실패 행 제거.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="45" customHeight="1">
+      <c r="A106" s="8" t="n"/>
+      <c r="B106" s="9" t="n"/>
+      <c r="C106" s="9" t="n"/>
+      <c r="D106" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr"/>
+      <c r="F106" s="9" t="inlineStr"/>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>leadership_comments.csv: 강점·개선점이 둘 다 공란인 행은 저장하지 않음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="45" customHeight="1">
+      <c r="A107" s="8" t="n"/>
+      <c r="B107" s="9" t="n"/>
+      <c r="C107" s="9" t="n"/>
+      <c r="D107" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr"/>
+      <c r="F107" s="9" t="inlineStr"/>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>같은 (researcher_id,year,evaluator_group) 내 여러 평가자는 '평균'으로 합쳐짐(첫 값 채택 아님) — 그룹당 1행.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="45" customHeight="1">
+      <c r="A108" s="8" t="n"/>
+      <c r="B108" s="9" t="n"/>
+      <c r="C108" s="9" t="n"/>
+      <c r="D108" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr"/>
+      <c r="F108" s="9" t="inlineStr"/>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>leadership.csv: write_merged() TABLE_KEYS['leadership'] upsert. leadership_comments.csv: write_merged(group_replace=True) — 동일 (researcher_id,year,group) 블록 전체를 이번 실행 결과로 통째 교체.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B109" s="19" t="inlineStr">
+        <is>
+          <t>핵심이력</t>
+        </is>
+      </c>
+      <c r="C109" s="19" t="inlineStr">
+        <is>
+          <t>process_incentive.py</t>
+        </is>
+      </c>
+      <c r="D109" s="19" t="n"/>
+      <c r="E109" s="19" t="n"/>
+      <c r="F109" s="19" t="n"/>
+      <c r="G109" s="19" t="n"/>
+    </row>
+    <row r="110" ht="45" customHeight="1">
+      <c r="A110" s="8" t="n"/>
+      <c r="B110" s="9" t="n"/>
+      <c r="C110" s="9" t="n"/>
+      <c r="D110" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G110" s="9" t="inlineStr">
+        <is>
+          <t>norm_id(); 빈 값 제거.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="45" customHeight="1">
+      <c r="A111" s="8" t="n"/>
+      <c r="B111" s="9" t="n"/>
+      <c r="C111" s="9" t="n"/>
+      <c r="D111" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>'22'</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>year=2022 / selected / category</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>셀 값이 있으면 selected=True, category=그 셀 텍스트 그대로; 비면 selected=False, category=''.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="45" customHeight="1">
+      <c r="A112" s="8" t="n"/>
+      <c r="B112" s="9" t="n"/>
+      <c r="C112" s="9" t="n"/>
+      <c r="D112" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>'23'~'26'</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>year=2023~2026 / selected / category</t>
+        </is>
+      </c>
+      <c r="G112" s="9" t="inlineStr">
+        <is>
+          <t>'22'와 동일한 변환, YEAR_COLS 매핑에 정의된 존재하는 연도 컬럼만 처리.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="45" customHeight="1">
+      <c r="A113" s="8" t="n"/>
+      <c r="B113" s="9" t="n"/>
+      <c r="C113" s="9" t="n"/>
+      <c r="D113" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>(컬럼 위치 자체)</t>
+        </is>
+      </c>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="G113" s="9" t="inlineStr">
+        <is>
+          <t>셀 값이 아니라 그 값이 들어있던 컬럼 헤더(연도)에서 파생.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="45" customHeight="1">
+      <c r="A114" s="8" t="n"/>
+      <c r="B114" s="9" t="n"/>
+      <c r="C114" s="9" t="n"/>
+      <c r="D114" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>(셀 유무)</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>빈 값 여부(is_blank)만으로 계산되는 불리언.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="45" customHeight="1">
+      <c r="A115" s="8" t="n"/>
+      <c r="B115" s="9" t="n"/>
+      <c r="C115" s="9" t="n"/>
+      <c r="D115" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>(셀 재사용)</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>selected를 만든 그 셀 텍스트를 그대로 재사용 — 물리적으로 1개 셀이 2개 출력 필드(selected+category)를 만듦.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="45" customHeight="1">
+      <c r="A116" s="8" t="n"/>
+      <c r="B116" s="9" t="n"/>
+      <c r="C116" s="9" t="n"/>
+      <c r="D116" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>(하드코딩)</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="G116" s="9" t="inlineStr">
+        <is>
+          <t>모든 행에 대해 항상 빈 문자열.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="45" customHeight="1">
+      <c r="A117" s="8" t="n"/>
+      <c r="B117" s="9" t="n"/>
+      <c r="C117" s="9" t="n"/>
+      <c r="D117" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr"/>
+      <c r="F117" s="9" t="inlineStr"/>
+      <c r="G117" s="9" t="inlineStr">
+        <is>
+          <t>wide→long 변환 — 사람 1행이 최대 5행(연도별)으로 펼쳐짐. 5개 연도 컬럼이 파일에 하나도 없으면 전체 중단.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="45" customHeight="1">
+      <c r="A118" s="8" t="n"/>
+      <c r="B118" s="9" t="n"/>
+      <c r="C118" s="9" t="n"/>
+      <c r="D118" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr"/>
+      <c r="F118" s="9" t="inlineStr"/>
+      <c r="G118" s="9" t="inlineStr">
+        <is>
+          <t>사번 빈 행 제거. researcher_id, year 순 정렬 후 write_merged() TABLE_KEYS['incentive_selection'] upsert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B119" s="19" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="C119" s="19" t="inlineStr">
+        <is>
+          <t>process_publications.py</t>
+        </is>
+      </c>
+      <c r="D119" s="19" t="n"/>
+      <c r="E119" s="19" t="n"/>
+      <c r="F119" s="19" t="n"/>
+      <c r="G119" s="19" t="n"/>
+    </row>
+    <row r="120" ht="45" customHeight="1">
+      <c r="A120" s="8" t="n"/>
+      <c r="B120" s="9" t="n"/>
+      <c r="C120" s="9" t="n"/>
+      <c r="D120" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>norm_id(); 빈 값 제거. 필수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="45" customHeight="1">
+      <c r="A121" s="8" t="n"/>
+      <c r="B121" s="9" t="n"/>
+      <c r="C121" s="9" t="n"/>
+      <c r="D121" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>저자구분</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>author_type</t>
+        </is>
+      </c>
+      <c r="G121" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="45" customHeight="1">
+      <c r="A122" s="8" t="n"/>
+      <c r="B122" s="9" t="n"/>
+      <c r="C122" s="9" t="n"/>
+      <c r="D122" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>교신저자여부</t>
+        </is>
+      </c>
+      <c r="F122" s="9" t="inlineStr">
+        <is>
+          <t>is_corresponding</t>
+        </is>
+      </c>
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>소문자화 후 {'y','yes','예','o','○','1','true','교신'} 포함이면 True.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="45" customHeight="1">
+      <c r="A123" s="8" t="n"/>
+      <c r="B123" s="9" t="n"/>
+      <c r="C123" s="9" t="n"/>
+      <c r="D123" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>논문제목</t>
+        </is>
+      </c>
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="G123" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="45" customHeight="1">
+      <c r="A124" s="8" t="n"/>
+      <c r="B124" s="9" t="n"/>
+      <c r="C124" s="9" t="n"/>
+      <c r="D124" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>게재/발표처</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="G124" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="45" customHeight="1">
+      <c r="A125" s="8" t="n"/>
+      <c r="B125" s="9" t="n"/>
+      <c r="C125" s="9" t="n"/>
+      <c r="D125" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="inlineStr">
+        <is>
+          <t>발표형태</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>pub_type</t>
+        </is>
+      </c>
+      <c r="G125" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="45" customHeight="1">
+      <c r="A126" s="8" t="n"/>
+      <c r="B126" s="9" t="n"/>
+      <c r="C126" s="9" t="n"/>
+      <c r="D126" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>진행상태</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>paper_status</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>원본 텍스트 trim 그대로 저장. 동시에 공백제거+대문자화한 정규화값이 {'최종완료','ACCEPT완료'}인지로 행 유효성 필터에도 사용됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="45" customHeight="1">
+      <c r="A127" s="8" t="n"/>
+      <c r="B127" s="9" t="n"/>
+      <c r="C127" s="9" t="n"/>
+      <c r="D127" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>발표일</t>
+        </is>
+      </c>
+      <c r="F127" s="9" t="inlineStr">
+        <is>
+          <t>announce_date</t>
+        </is>
+      </c>
+      <c r="G127" s="9" t="inlineStr">
+        <is>
+          <t>parse_yyyymmdd(). pub_date가 비었을 때 대체값으로도 사용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="45" customHeight="1">
+      <c r="A128" s="8" t="n"/>
+      <c r="B128" s="9" t="n"/>
+      <c r="C128" s="9" t="n"/>
+      <c r="D128" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>실적일</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr">
+        <is>
+          <t>pub_date (1순위)</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>parse_yyyymmdd(); 비면 발표일 파싱 값으로 대체.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="45" customHeight="1">
+      <c r="A129" s="8" t="n"/>
+      <c r="B129" s="9" t="n"/>
+      <c r="C129" s="9" t="n"/>
+      <c r="D129" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>저자순위</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>author_rank</t>
+        </is>
+      </c>
+      <c r="G129" s="9" t="inlineStr">
+        <is>
+          <t>_parse_int(): 정수 변환(소수 버림), 실패 시 공란.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="45" customHeight="1">
+      <c r="A130" s="8" t="n"/>
+      <c r="B130" s="9" t="n"/>
+      <c r="C130" s="9" t="n"/>
+      <c r="D130" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>총저자수</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="inlineStr">
+        <is>
+          <t>total_authors</t>
+        </is>
+      </c>
+      <c r="G130" s="9" t="inlineStr">
+        <is>
+          <t>author_rank와 동일.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="45" customHeight="1">
+      <c r="A131" s="8" t="n"/>
+      <c r="B131" s="9" t="n"/>
+      <c r="C131" s="9" t="n"/>
+      <c r="D131" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>전체 저자정보</t>
+        </is>
+      </c>
+      <c r="F131" s="9" t="inlineStr">
+        <is>
+          <t>author_info</t>
+        </is>
+      </c>
+      <c r="G131" s="9" t="inlineStr">
+        <is>
+          <t>_strip_contribution(): 끝의 '(기여도 : XX%)' 부분만 정규식 제거한 나머지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="45" customHeight="1">
+      <c r="A132" s="8" t="n"/>
+      <c r="B132" s="9" t="n"/>
+      <c r="C132" s="9" t="n"/>
+      <c r="D132" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>전체 저자정보 (동일 컬럼, 2개 출력)</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>contribution</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>같은 원본 컬럼에서 정규식으로 '(기여도 : XX%)'의 숫자만 추출 — author_info와 같은 셀에서 파생되는 별도 필드.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="45" customHeight="1">
+      <c r="A133" s="8" t="n"/>
+      <c r="B133" s="9" t="n"/>
+      <c r="C133" s="9" t="n"/>
+      <c r="D133" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="inlineStr">
+        <is>
+          <t>과제명</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="inlineStr">
+        <is>
+          <t>project_name</t>
+        </is>
+      </c>
+      <c r="G133" s="9" t="inlineStr">
+        <is>
+          <t>trim만(선택, 없으면 공란).</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="45" customHeight="1">
+      <c r="A134" s="8" t="n"/>
+      <c r="B134" s="9" t="n"/>
+      <c r="C134" s="9" t="n"/>
+      <c r="D134" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>과제코드</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>project_code</t>
+        </is>
+      </c>
+      <c r="G134" s="9" t="inlineStr">
+        <is>
+          <t>trim만(선택).</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="45" customHeight="1">
+      <c r="A135" s="8" t="n"/>
+      <c r="B135" s="9" t="n"/>
+      <c r="C135" s="9" t="n"/>
+      <c r="D135" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="inlineStr">
+        <is>
+          <t>(2개 컬럼 fallback)</t>
+        </is>
+      </c>
+      <c r="F135" s="9" t="inlineStr">
+        <is>
+          <t>pub_date</t>
+        </is>
+      </c>
+      <c r="G135" s="9" t="inlineStr">
+        <is>
+          <t>실적일 우선, 없으면 발표일로 대체한 2차 값.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="45" customHeight="1">
+      <c r="A136" s="8" t="n"/>
+      <c r="B136" s="9" t="n"/>
+      <c r="C136" s="9" t="n"/>
+      <c r="D136" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>(pub_date에서 재파생)</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="inlineStr">
+        <is>
+          <t>pub_year</t>
+        </is>
+      </c>
+      <c r="G136" s="9" t="inlineStr">
+        <is>
+          <t>pub_date 문자열의 앞 4자리(pub_date 자체가 이미 2개 컬럼 fallback 결과라 3차 파생값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="45" customHeight="1">
+      <c r="A137" s="8" t="n"/>
+      <c r="B137" s="9" t="n"/>
+      <c r="C137" s="9" t="n"/>
+      <c r="D137" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="inlineStr"/>
+      <c r="F137" s="9" t="inlineStr"/>
+      <c r="G137" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id 빈 행 제거.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="45" customHeight="1">
+      <c r="A138" s="8" t="n"/>
+      <c r="B138" s="9" t="n"/>
+      <c r="C138" s="9" t="n"/>
+      <c r="D138" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr"/>
+      <c r="F138" s="9" t="inlineStr"/>
+      <c r="G138" s="9" t="inlineStr">
+        <is>
+          <t>핵심 필터: 진행상태 정규화값이 {'최종완료','ACCEPT완료'} 중 하나이고 동시에 pub_date가 비어있지 않은 행만 유지 — 둘 중 하나라도 안 맞으면 그 행 전체 제외.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="45" customHeight="1">
+      <c r="A139" s="8" t="n"/>
+      <c r="B139" s="9" t="n"/>
+      <c r="C139" s="9" t="n"/>
+      <c r="D139" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E139" s="9" t="inlineStr"/>
+      <c r="F139" s="9" t="inlineStr"/>
+      <c r="G139" s="9" t="inlineStr">
+        <is>
+          <t>필수 컬럼(REQUIRED_COLS) 중 하나라도 없으면 전체 중단.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="45" customHeight="1">
+      <c r="A140" s="8" t="n"/>
+      <c r="B140" s="9" t="n"/>
+      <c r="C140" s="9" t="n"/>
+      <c r="D140" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr"/>
+      <c r="F140" s="9" t="inlineStr"/>
+      <c r="G140" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id 오름차순, pub_date 내림차순 정렬 후 write_merged() TABLE_KEYS['publications'] upsert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B141" s="19" t="inlineStr">
+        <is>
+          <t>인물 코멘트</t>
+        </is>
+      </c>
+      <c r="C141" s="19" t="inlineStr">
+        <is>
+          <t>process_comments.py</t>
+        </is>
+      </c>
+      <c r="D141" s="19" t="n"/>
+      <c r="E141" s="19" t="n"/>
+      <c r="F141" s="19" t="n"/>
+      <c r="G141" s="19" t="n"/>
+    </row>
+    <row r="142" ht="45" customHeight="1">
+      <c r="A142" s="8" t="n"/>
+      <c r="B142" s="9" t="n"/>
+      <c r="C142" s="9" t="n"/>
+      <c r="D142" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E142" s="9" t="inlineStr"/>
+      <c r="F142" s="9" t="inlineStr"/>
+      <c r="G142" s="9" t="inlineStr">
+        <is>
+          <t>1차 원천(data/raw/comments_raw.xlsx)은 현재 실존하지 않음 — read_source('comments')가 None을 반환하면 [SKIP] 로그만 남기고 이 소스 처리 자체를 건너뜀(전체 파이프라인은 계속 진행). 아래는 그 파일이 존재할 경우의 처리 방식(코드상 정의돼 있으나 현재는 미가동).</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="45" customHeight="1">
+      <c r="A143" s="8" t="n"/>
+      <c r="B143" s="9" t="n"/>
+      <c r="C143" s="9" t="n"/>
+      <c r="D143" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E143" s="9" t="inlineStr">
+        <is>
+          <t>(norm_researcher_id_col()이 정규화 — 원본 한글 헤더명은 이 정규화 이전 단계라 불명)</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G143" s="9" t="inlineStr">
+        <is>
+          <t>str() 캐스팅. 필수 — 없으면 WARN 후 이 소스 스킵.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="45" customHeight="1">
+      <c r="A144" s="8" t="n"/>
+      <c r="B144" s="9" t="n"/>
+      <c r="C144" s="9" t="n"/>
+      <c r="D144" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr">
+        <is>
+          <t>그대로 passthrough(별도 파싱 없음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="45" customHeight="1">
+      <c r="A145" s="8" t="n"/>
+      <c r="B145" s="9" t="n"/>
+      <c r="C145" s="9" t="n"/>
+      <c r="D145" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="inlineStr">
+        <is>
+          <t>comment_raw</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="inlineStr">
+        <is>
+          <t>comment_raw</t>
+        </is>
+      </c>
+      <c r="G145" s="9" t="inlineStr">
+        <is>
+          <t>str() 캐스팅, 원문 그대로(LLM 요약 입력으로도 사용).</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="45" customHeight="1">
+      <c r="A146" s="8" t="n"/>
+      <c r="B146" s="9" t="n"/>
+      <c r="C146" s="9" t="n"/>
+      <c r="D146" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E146" s="9" t="inlineStr">
+        <is>
+          <t>commenter_type (선택)</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="inlineStr">
+        <is>
+          <t>commenter_type</t>
+        </is>
+      </c>
+      <c r="G146" s="9" t="inlineStr">
+        <is>
+          <t>있으면 str(), 없으면 하드코딩 기본값 '부서장'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="45" customHeight="1">
+      <c r="A147" s="8" t="n"/>
+      <c r="B147" s="9" t="n"/>
+      <c r="C147" s="9" t="n"/>
+      <c r="D147" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E147" s="9" t="inlineStr">
+        <is>
+          <t>comment_summary (선택)</t>
+        </is>
+      </c>
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>comment_summary</t>
+        </is>
+      </c>
+      <c r="G147" s="9" t="inlineStr">
+        <is>
+          <t>non-LLM 모드: 있으면 그대로, 없으면 comment_raw[:120]+'...'. --llm 모드: LLM 재생성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="45" customHeight="1">
+      <c r="A148" s="8" t="n"/>
+      <c r="B148" s="9" t="n"/>
+      <c r="C148" s="9" t="n"/>
+      <c r="D148" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E148" s="9" t="inlineStr">
+        <is>
+          <t>strengths (선택)</t>
+        </is>
+      </c>
+      <c r="F148" s="9" t="inlineStr">
+        <is>
+          <t>strengths</t>
+        </is>
+      </c>
+      <c r="G148" s="9" t="inlineStr">
+        <is>
+          <t>non-LLM: 있으면 그대로/없으면 공란. --llm: LLM 생성값.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="45" customHeight="1">
+      <c r="A149" s="8" t="n"/>
+      <c r="B149" s="9" t="n"/>
+      <c r="C149" s="9" t="n"/>
+      <c r="D149" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E149" s="9" t="inlineStr">
+        <is>
+          <t>improvements (선택)</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr">
+        <is>
+          <t>improvements</t>
+        </is>
+      </c>
+      <c r="G149" s="9" t="inlineStr">
+        <is>
+          <t>strengths와 동일.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="45" customHeight="1">
+      <c r="A150" s="8" t="n"/>
+      <c r="B150" s="9" t="n"/>
+      <c r="C150" s="9" t="n"/>
+      <c r="D150" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E150" s="9" t="inlineStr">
+        <is>
+          <t>(2차 입력, process_leadership.py 산출물)</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="inlineStr">
+        <is>
+          <t>leadership_comments.csv 전체 컬럼 concat</t>
+        </is>
+      </c>
+      <c r="G150" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id/year/commenter_type/comment_raw/comment_summary/strengths/improvements를 그대로 이어붙임(researcher_id만 zfill(8) 재정규화). 현재 comments.csv는 사실상 이 병합만으로 채워짐(1차 원천 부재).</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="45" customHeight="1">
+      <c r="A151" s="8" t="n"/>
+      <c r="B151" s="9" t="n"/>
+      <c r="C151" s="9" t="n"/>
+      <c r="D151" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E151" s="9" t="inlineStr">
+        <is>
+          <t>(하드코딩 기본값)</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr">
+        <is>
+          <t>commenter_type='부서장'</t>
+        </is>
+      </c>
+      <c r="G151" s="9" t="inlineStr">
+        <is>
+          <t>comments_raw 소스에 그룹 정보가 없을 때의 기본값.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="45" customHeight="1">
+      <c r="A152" s="8" t="n"/>
+      <c r="B152" s="9" t="n"/>
+      <c r="C152" s="9" t="n"/>
+      <c r="D152" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>(LLM, --llm 모드만)</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>comment_summary/strengths/improvements</t>
+        </is>
+      </c>
+      <c r="G152" s="9" t="inlineStr">
+        <is>
+          <t>comment_raw만 LLM에 투입(researcher_id/이름 등 식별정보 절대 미포함)해 JSON 응답으로 재생성. 실패 시 comment_summary는 앞 120자 폴백, 나머지는 공란.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="45" customHeight="1">
+      <c r="A153" s="8" t="n"/>
+      <c r="B153" s="9" t="n"/>
+      <c r="C153" s="9" t="n"/>
+      <c r="D153" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>(완전 합성 행, --llm 모드만)</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>commenter_type='종합요약'</t>
+        </is>
+      </c>
+      <c r="G153" s="9" t="inlineStr">
+        <is>
+          <t>한 연구원의 모든 부서장 코멘트+모든 리더십_* strengths/improvements를 하나로 합쳐 LLM 재투입한 연구원 단위 요약 행. year는 관련 행들 중 최댓값(가장 최근 연도).</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="45" customHeight="1">
+      <c r="A154" s="8" t="n"/>
+      <c r="B154" s="9" t="n"/>
+      <c r="C154" s="9" t="n"/>
+      <c r="D154" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr"/>
+      <c r="F154" s="9" t="inlineStr"/>
+      <c r="G154" s="9" t="inlineStr">
+        <is>
+          <t>comments_raw 소스에 필수 컬럼(researcher_id/year/comment_raw) 중 하나라도 없으면 WARN 후 그 소스만 스킵(leadership_comments 병합은 계속 진행).</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="45" customHeight="1">
+      <c r="A155" s="8" t="n"/>
+      <c r="B155" s="9" t="n"/>
+      <c r="C155" s="9" t="n"/>
+      <c r="D155" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="inlineStr"/>
+      <c r="F155" s="9" t="inlineStr"/>
+      <c r="G155" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id, commenter_type, year 순 정렬 후 write_merged() TABLE_KEYS['comments'] upsert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B156" s="19" t="inlineStr">
+        <is>
+          <t>인사발령</t>
+        </is>
+      </c>
+      <c r="C156" s="19" t="inlineStr">
+        <is>
+          <t>process_personnel_orders.py</t>
+        </is>
+      </c>
+      <c r="D156" s="19" t="n"/>
+      <c r="E156" s="19" t="n"/>
+      <c r="F156" s="19" t="n"/>
+      <c r="G156" s="19" t="n"/>
+    </row>
+    <row r="157" ht="45" customHeight="1">
+      <c r="A157" s="8" t="n"/>
+      <c r="B157" s="9" t="n"/>
+      <c r="C157" s="9" t="n"/>
+      <c r="D157" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E157" s="9" t="inlineStr">
+        <is>
+          <t>사원번호</t>
+        </is>
+      </c>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G157" s="9" t="inlineStr">
+        <is>
+          <t>norm_id() 8자리.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="45" customHeight="1">
+      <c r="A158" s="8" t="n"/>
+      <c r="B158" s="9" t="n"/>
+      <c r="C158" s="9" t="n"/>
+      <c r="D158" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E158" s="9" t="inlineStr">
+        <is>
+          <t>발령일자</t>
+        </is>
+      </c>
+      <c r="F158" s="9" t="inlineStr">
+        <is>
+          <t>order_date</t>
+        </is>
+      </c>
+      <c r="G158" s="9" t="inlineStr">
+        <is>
+          <t>parse_yyyymmdd() → YYYY-MM-DD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="45" customHeight="1">
+      <c r="A159" s="8" t="n"/>
+      <c r="B159" s="9" t="n"/>
+      <c r="C159" s="9" t="n"/>
+      <c r="D159" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E159" s="9" t="inlineStr">
+        <is>
+          <t>발령명</t>
+        </is>
+      </c>
+      <c r="F159" s="9" t="inlineStr">
+        <is>
+          <t>order_name</t>
+        </is>
+      </c>
+      <c r="G159" s="9" t="inlineStr">
+        <is>
+          <t>trim만(컬럼 없으면 공란).</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="45" customHeight="1">
+      <c r="A160" s="8" t="n"/>
+      <c r="B160" s="9" t="n"/>
+      <c r="C160" s="9" t="n"/>
+      <c r="D160" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E160" s="9" t="inlineStr">
+        <is>
+          <t>부서</t>
+        </is>
+      </c>
+      <c r="F160" s="9" t="inlineStr">
+        <is>
+          <t>order_dep</t>
+        </is>
+      </c>
+      <c r="G160" s="9" t="inlineStr">
+        <is>
+          <t>trim만(컬럼 없으면 공란).</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="45" customHeight="1">
+      <c r="A161" s="8" t="n"/>
+      <c r="B161" s="9" t="n"/>
+      <c r="C161" s="9" t="n"/>
+      <c r="D161" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E161" s="9" t="inlineStr">
+        <is>
+          <t>직급명</t>
+        </is>
+      </c>
+      <c r="F161" s="9" t="inlineStr">
+        <is>
+          <t>order_cl</t>
+        </is>
+      </c>
+      <c r="G161" s="9" t="inlineStr">
+        <is>
+          <t>_strip_paren(): 괄호와 그 안 내용 제거(예: '선임연구원(과장)'→'선임연구원')(컬럼 없으면 공란).</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="45" customHeight="1">
+      <c r="A162" s="8" t="n"/>
+      <c r="B162" s="9" t="n"/>
+      <c r="C162" s="9" t="n"/>
+      <c r="D162" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E162" s="9" t="inlineStr">
+        <is>
+          <t>직책명</t>
+        </is>
+      </c>
+      <c r="F162" s="9" t="inlineStr">
+        <is>
+          <t>order_assignment</t>
+        </is>
+      </c>
+      <c r="G162" s="9" t="inlineStr">
+        <is>
+          <t>trim만(컬럼 없으면 공란).</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="45" customHeight="1">
+      <c r="A163" s="8" t="n"/>
+      <c r="B163" s="9" t="n"/>
+      <c r="C163" s="9" t="n"/>
+      <c r="D163" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E163" s="9" t="inlineStr"/>
+      <c r="F163" s="9" t="inlineStr"/>
+      <c r="G163" s="9" t="inlineStr">
+        <is>
+          <t>사원번호/발령일자 필수(없으면 중단). researcher_id 빈 행 제거.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="45" customHeight="1">
+      <c r="A164" s="8" t="n"/>
+      <c r="B164" s="9" t="n"/>
+      <c r="C164" s="9" t="n"/>
+      <c r="D164" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E164" s="9" t="inlineStr"/>
+      <c r="F164" s="9" t="inlineStr"/>
+      <c r="G164" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id, order_date 순 정렬 후 write_merged() TABLE_KEYS['hr_orders'] upsert(시점보호·이력테이블 없음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="20" customHeight="1">
+      <c r="A165" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B165" s="19" t="inlineStr">
+        <is>
+          <t>과제정보</t>
+        </is>
+      </c>
+      <c r="C165" s="19" t="inlineStr">
+        <is>
+          <t>process_task_information.py</t>
+        </is>
+      </c>
+      <c r="D165" s="19" t="n"/>
+      <c r="E165" s="19" t="n"/>
+      <c r="F165" s="19" t="n"/>
+      <c r="G165" s="19" t="n"/>
+    </row>
+    <row r="166" ht="45" customHeight="1">
+      <c r="A166" s="8" t="n"/>
+      <c r="B166" s="9" t="n"/>
+      <c r="C166" s="9" t="n"/>
+      <c r="D166" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E166" s="9" t="inlineStr">
+        <is>
+          <t>과제명</t>
+        </is>
+      </c>
+      <c r="F166" s="9" t="inlineStr">
+        <is>
+          <t>task_name</t>
+        </is>
+      </c>
+      <c r="G166" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="45" customHeight="1">
+      <c r="A167" s="8" t="n"/>
+      <c r="B167" s="9" t="n"/>
+      <c r="C167" s="9" t="n"/>
+      <c r="D167" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E167" s="9" t="inlineStr">
+        <is>
+          <t>과제코드</t>
+        </is>
+      </c>
+      <c r="F167" s="9" t="inlineStr">
+        <is>
+          <t>task_code</t>
+        </is>
+      </c>
+      <c r="G167" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="45" customHeight="1">
+      <c r="A168" s="8" t="n"/>
+      <c r="B168" s="9" t="n"/>
+      <c r="C168" s="9" t="n"/>
+      <c r="D168" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E168" s="9" t="inlineStr">
+        <is>
+          <t>관계사</t>
+        </is>
+      </c>
+      <c r="F168" s="9" t="inlineStr">
+        <is>
+          <t>task_collabo</t>
+        </is>
+      </c>
+      <c r="G168" s="9" t="inlineStr">
+        <is>
+          <t>trim 후 저장 직전 excel_safe_text() 적용(=,-,+,@ 시작값의 수식 오인 방지).</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="45" customHeight="1">
+      <c r="A169" s="8" t="n"/>
+      <c r="B169" s="9" t="n"/>
+      <c r="C169" s="9" t="n"/>
+      <c r="D169" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E169" s="9" t="inlineStr">
+        <is>
+          <t>개요_목표(수행목적)</t>
+        </is>
+      </c>
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>task_goal</t>
+        </is>
+      </c>
+      <c r="G169" s="9" t="inlineStr">
+        <is>
+          <t>trim + excel_safe_text().</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="45" customHeight="1">
+      <c r="A170" s="8" t="n"/>
+      <c r="B170" s="9" t="n"/>
+      <c r="C170" s="9" t="n"/>
+      <c r="D170" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E170" s="9" t="inlineStr">
+        <is>
+          <t>개요_가치</t>
+        </is>
+      </c>
+      <c r="F170" s="9" t="inlineStr">
+        <is>
+          <t>task_value</t>
+        </is>
+      </c>
+      <c r="G170" s="9" t="inlineStr">
+        <is>
+          <t>trim + excel_safe_text().</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="45" customHeight="1">
+      <c r="A171" s="8" t="n"/>
+      <c r="B171" s="9" t="n"/>
+      <c r="C171" s="9" t="n"/>
+      <c r="D171" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E171" s="9" t="inlineStr">
+        <is>
+          <t>개요_확보전략(목표)</t>
+        </is>
+      </c>
+      <c r="F171" s="9" t="inlineStr">
+        <is>
+          <t>task_howtoget</t>
+        </is>
+      </c>
+      <c r="G171" s="9" t="inlineStr">
+        <is>
+          <t>trim + excel_safe_text().</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="45" customHeight="1">
+      <c r="A172" s="8" t="n"/>
+      <c r="B172" s="9" t="n"/>
+      <c r="C172" s="9" t="n"/>
+      <c r="D172" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E172" s="9" t="inlineStr">
+        <is>
+          <t>개요_예상문제</t>
+        </is>
+      </c>
+      <c r="F172" s="9" t="inlineStr">
+        <is>
+          <t>task_expectissue</t>
+        </is>
+      </c>
+      <c r="G172" s="9" t="inlineStr">
+        <is>
+          <t>trim + excel_safe_text().</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="45" customHeight="1">
+      <c r="A173" s="8" t="n"/>
+      <c r="B173" s="9" t="n"/>
+      <c r="C173" s="9" t="n"/>
+      <c r="D173" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E173" s="9" t="inlineStr">
+        <is>
+          <t>개요_주요 활용 Activity 계획</t>
+        </is>
+      </c>
+      <c r="F173" s="9" t="inlineStr">
+        <is>
+          <t>task_Activityplan</t>
+        </is>
+      </c>
+      <c r="G173" s="9" t="inlineStr">
+        <is>
+          <t>trim + excel_safe_text().</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="45" customHeight="1">
+      <c r="A174" s="8" t="n"/>
+      <c r="B174" s="9" t="n"/>
+      <c r="C174" s="9" t="n"/>
+      <c r="D174" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E174" s="9" t="inlineStr">
+        <is>
+          <t>개요_향후활용계획(향후계획)</t>
+        </is>
+      </c>
+      <c r="F174" s="9" t="inlineStr">
+        <is>
+          <t>task_futureusage</t>
+        </is>
+      </c>
+      <c r="G174" s="9" t="inlineStr">
+        <is>
+          <t>trim + excel_safe_text().</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="45" customHeight="1">
+      <c r="A175" s="8" t="n"/>
+      <c r="B175" s="9" t="n"/>
+      <c r="C175" s="9" t="n"/>
+      <c r="D175" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E175" s="9" t="inlineStr">
+        <is>
+          <t>작성일</t>
+        </is>
+      </c>
+      <c r="F175" s="9" t="inlineStr">
+        <is>
+          <t>write_date</t>
+        </is>
+      </c>
+      <c r="G175" s="9" t="inlineStr">
+        <is>
+          <t>parse_yyyymmdd() → YYYY-MM-DD — 이 값이 process_tasks.py의 과제명 개명 이력 판정 기준시각으로 재사용됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="45" customHeight="1">
+      <c r="A176" s="8" t="n"/>
+      <c r="B176" s="9" t="n"/>
+      <c r="C176" s="9" t="n"/>
+      <c r="D176" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E176" s="9" t="inlineStr"/>
+      <c r="F176" s="9" t="inlineStr"/>
+      <c r="G176" s="9" t="inlineStr">
+        <is>
+          <t>과제명/과제코드/작성일 중 하나라도 없으면 전체 중단.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="45" customHeight="1">
+      <c r="A177" s="8" t="n"/>
+      <c r="B177" s="9" t="n"/>
+      <c r="C177" s="9" t="n"/>
+      <c r="D177" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E177" s="9" t="inlineStr"/>
+      <c r="F177" s="9" t="inlineStr"/>
+      <c r="G177" s="9" t="inlineStr">
+        <is>
+          <t>task_name 기준 dedup(_dedupe_by_name, task_code 기준 아님 — 개명 이력 보존 목적): (1) 7개 본문 컬럼 중 채워진 개수(_filled_count) 계산 (2) [_filled_count, write_date] 오름차순 정렬 후 drop_duplicates(keep='last') — 즉 내용이 가장 풍부한 행 우선, 동률이면 write_date가 가장 오래된(=최초) 행 채택. (2026-09-09 버그 수정: 예전엔 최신 write_date를 남겨 재작성만 되고 내용은 그대로인 경우 개명 시점이 왜곡됐음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="45" customHeight="1">
+      <c r="A178" s="8" t="n"/>
+      <c r="B178" s="9" t="n"/>
+      <c r="C178" s="9" t="n"/>
+      <c r="D178" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E178" s="9" t="inlineStr"/>
+      <c r="F178" s="9" t="inlineStr"/>
+      <c r="G178" s="9" t="inlineStr">
+        <is>
+          <t>같은 task_code라도 task_name이 다르면 별도 행으로 유지(collapse 안 함) — process_tasks.py가 이 이력을 그대로 조회해야 하므로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="45" customHeight="1">
+      <c r="A179" s="8" t="n"/>
+      <c r="B179" s="9" t="n"/>
+      <c r="C179" s="9" t="n"/>
+      <c r="D179" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E179" s="9" t="inlineStr"/>
+      <c r="F179" s="9" t="inlineStr"/>
+      <c r="G179" s="9" t="inlineStr">
+        <is>
+          <t>task_name 정렬 후 write_merged() TABLE_KEYS['tasks_information'] upsert(시점보호·이력테이블 없음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B180" s="19" t="inlineStr">
+        <is>
+          <t>핵심기술</t>
+        </is>
+      </c>
+      <c r="C180" s="19" t="inlineStr">
+        <is>
+          <t>process_core_technology.py</t>
+        </is>
+      </c>
+      <c r="D180" s="19" t="n"/>
+      <c r="E180" s="19" t="n"/>
+      <c r="F180" s="19" t="n"/>
+      <c r="G180" s="19" t="n"/>
+    </row>
+    <row r="181" ht="45" customHeight="1">
+      <c r="A181" s="8" t="n"/>
+      <c r="B181" s="9" t="n"/>
+      <c r="C181" s="9" t="n"/>
+      <c r="D181" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E181" s="9" t="inlineStr">
+        <is>
+          <t>사원번호</t>
+        </is>
+      </c>
+      <c r="F181" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G181" s="9" t="inlineStr">
+        <is>
+          <t>norm_id().</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="45" customHeight="1">
+      <c r="A182" s="8" t="n"/>
+      <c r="B182" s="9" t="n"/>
+      <c r="C182" s="9" t="n"/>
+      <c r="D182" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E182" s="9" t="inlineStr">
+        <is>
+          <t>기술 분야</t>
+        </is>
+      </c>
+      <c r="F182" s="9" t="inlineStr">
+        <is>
+          <t>tech_field</t>
+        </is>
+      </c>
+      <c r="G182" s="9" t="inlineStr">
+        <is>
+          <t>NA→'', trim(컬럼 없으면 공란).</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="45" customHeight="1">
+      <c r="A183" s="8" t="n"/>
+      <c r="B183" s="9" t="n"/>
+      <c r="C183" s="9" t="n"/>
+      <c r="D183" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E183" s="9" t="inlineStr">
+        <is>
+          <t>핵심기술</t>
+        </is>
+      </c>
+      <c r="F183" s="9" t="inlineStr">
+        <is>
+          <t>tech_name</t>
+        </is>
+      </c>
+      <c r="G183" s="9" t="inlineStr">
+        <is>
+          <t>NA→'', trim(컬럼 없으면 공란).</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="45" customHeight="1">
+      <c r="A184" s="8" t="n"/>
+      <c r="B184" s="9" t="n"/>
+      <c r="C184" s="9" t="n"/>
+      <c r="D184" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E184" s="9" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="F184" s="9" t="inlineStr">
+        <is>
+          <t>tech_grade</t>
+        </is>
+      </c>
+      <c r="G184" s="9" t="inlineStr">
+        <is>
+          <t>NA→'', trim → 문자열 'nan'/'None' 치환 → 남은 빈 값은 전부 '-'로 대체.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="45" customHeight="1">
+      <c r="A185" s="8" t="n"/>
+      <c r="B185" s="9" t="n"/>
+      <c r="C185" s="9" t="n"/>
+      <c r="D185" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E185" s="9" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F185" s="9" t="inlineStr">
+        <is>
+          <t>valid_year, valid_month</t>
+        </is>
+      </c>
+      <c r="G185" s="9" t="inlineStr">
+        <is>
+          <t>process() 호출 시 valid_date 인자(기본 오늘)에서 계산, 원본 헤더 아님.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="45" customHeight="1">
+      <c r="A186" s="8" t="n"/>
+      <c r="B186" s="9" t="n"/>
+      <c r="C186" s="9" t="n"/>
+      <c r="D186" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E186" s="9" t="inlineStr"/>
+      <c r="F186" s="9" t="inlineStr"/>
+      <c r="G186" s="9" t="inlineStr">
+        <is>
+          <t>사원번호 없으면 중단. researcher_id 빈 행 제거.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="45" customHeight="1">
+      <c r="A187" s="8" t="n"/>
+      <c r="B187" s="9" t="n"/>
+      <c r="C187" s="9" t="n"/>
+      <c r="D187" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E187" s="9" t="inlineStr"/>
+      <c r="F187" s="9" t="inlineStr"/>
+      <c r="G187" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id 정렬 후 write_merged_with_valid_period(): 키=(researcher_id,tech_field,tech_name). 기존 저장 시점보다 이번 valid_date가 과거면 그 조합만 건너뜀(WARN). core_technology_history.csv에는 건너뛴 것 포함 항상 append.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="20" customHeight="1">
+      <c r="A188" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B188" s="19" t="inlineStr">
+        <is>
+          <t>보유기술</t>
+        </is>
+      </c>
+      <c r="C188" s="19" t="inlineStr">
+        <is>
+          <t>process_tech_ownership.py</t>
+        </is>
+      </c>
+      <c r="D188" s="19" t="n"/>
+      <c r="E188" s="19" t="n"/>
+      <c r="F188" s="19" t="n"/>
+      <c r="G188" s="19" t="n"/>
+    </row>
+    <row r="189" ht="45" customHeight="1">
+      <c r="A189" s="8" t="n"/>
+      <c r="B189" s="9" t="n"/>
+      <c r="C189" s="9" t="n"/>
+      <c r="D189" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E189" s="9" t="inlineStr">
+        <is>
+          <t>사원번호</t>
+        </is>
+      </c>
+      <c r="F189" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G189" s="9" t="inlineStr">
+        <is>
+          <t>norm_id().</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="45" customHeight="1">
+      <c r="A190" s="8" t="n"/>
+      <c r="B190" s="9" t="n"/>
+      <c r="C190" s="9" t="n"/>
+      <c r="D190" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E190" s="9" t="inlineStr">
+        <is>
+          <t>전문분야(1)~(5)</t>
+        </is>
+      </c>
+      <c r="F190" s="9" t="inlineStr">
+        <is>
+          <t>tech_1~tech_5</t>
+        </is>
+      </c>
+      <c r="G190" s="9" t="inlineStr">
+        <is>
+          <t>NA→'', trim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="45" customHeight="1">
+      <c r="A191" s="8" t="n"/>
+      <c r="B191" s="9" t="n"/>
+      <c r="C191" s="9" t="n"/>
+      <c r="D191" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E191" s="9" t="inlineStr">
+        <is>
+          <t>레벨(1)~(5)</t>
+        </is>
+      </c>
+      <c r="F191" s="9" t="inlineStr">
+        <is>
+          <t>lv_1~lv_5</t>
+        </is>
+      </c>
+      <c r="G191" s="9" t="inlineStr">
+        <is>
+          <t>trim 후 _clean_num(): 정수형 float의 소수점 제거(예: '3.0'→'3'); 비숫자/공란은 그대로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="45" customHeight="1">
+      <c r="A192" s="8" t="n"/>
+      <c r="B192" s="9" t="n"/>
+      <c r="C192" s="9" t="n"/>
+      <c r="D192" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E192" s="9" t="inlineStr">
+        <is>
+          <t>보유율(1)~(5)</t>
+        </is>
+      </c>
+      <c r="F192" s="9" t="inlineStr">
+        <is>
+          <t>portion_1~portion_5</t>
+        </is>
+      </c>
+      <c r="G192" s="9" t="inlineStr">
+        <is>
+          <t>trim 후 _scale_portion(): 0~1 비율값을 ×100해 정수면 정수문자열, 아니면 소수 1자리로 포맷.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="45" customHeight="1">
+      <c r="A193" s="8" t="n"/>
+      <c r="B193" s="9" t="n"/>
+      <c r="C193" s="9" t="n"/>
+      <c r="D193" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E193" s="9" t="inlineStr">
+        <is>
+          <t>E직군여부</t>
+        </is>
+      </c>
+      <c r="F193" s="9" t="inlineStr">
+        <is>
+          <t>E_support</t>
+        </is>
+      </c>
+      <c r="G193" s="9" t="inlineStr">
+        <is>
+          <t>_normalize_e_support(): 대문자화 값이 정확히 'E'면 'E', 그 외(공란/NaN 포함) 전부 'R'. 컬럼 자체가 없으면 전원 'R'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="45" customHeight="1">
+      <c r="A194" s="8" t="n"/>
+      <c r="B194" s="9" t="n"/>
+      <c r="C194" s="9" t="n"/>
+      <c r="D194" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E194" s="9" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F194" s="9" t="inlineStr">
+        <is>
+          <t>valid_year, valid_month</t>
+        </is>
+      </c>
+      <c r="G194" s="9" t="inlineStr">
+        <is>
+          <t>core_technology.py와 동일하게 valid_date 인자에서 계산.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="45" customHeight="1">
+      <c r="A195" s="8" t="n"/>
+      <c r="B195" s="9" t="n"/>
+      <c r="C195" s="9" t="n"/>
+      <c r="D195" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E195" s="9" t="inlineStr"/>
+      <c r="F195" s="9" t="inlineStr"/>
+      <c r="G195" s="9" t="inlineStr">
+        <is>
+          <t>사원번호 없으면 중단. researcher_id 빈 행 제거. 'nan'/'None' 문자열 잔재 정리.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="45" customHeight="1">
+      <c r="A196" s="8" t="n"/>
+      <c r="B196" s="9" t="n"/>
+      <c r="C196" s="9" t="n"/>
+      <c r="D196" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E196" s="9" t="inlineStr"/>
+      <c r="F196" s="9" t="inlineStr"/>
+      <c r="G196" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id 정렬 후 write_merged_with_valid_period(): 키=researcher_id(1인 1행). 기존 시점보다 과거면 그 사람 행만 건너뜀(WARN), tech_ownership_history.csv에는 항상 append.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="20" customHeight="1">
+      <c r="A197" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B197" s="19" t="inlineStr">
+        <is>
+          <t>직무이력</t>
+        </is>
+      </c>
+      <c r="C197" s="19" t="inlineStr">
+        <is>
+          <t>merge_job_profile_source.py (전처리) → process_job_profile.py</t>
+        </is>
+      </c>
+      <c r="D197" s="19" t="n"/>
+      <c r="E197" s="19" t="n"/>
+      <c r="F197" s="19" t="n"/>
+      <c r="G197" s="19" t="n"/>
+    </row>
+    <row r="198" ht="45" customHeight="1">
+      <c r="A198" s="8" t="n"/>
+      <c r="B198" s="9" t="n"/>
+      <c r="C198" s="9" t="n"/>
+      <c r="D198" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E198" s="9" t="inlineStr">
+        <is>
+          <t>(merge_job_profile_source.py)</t>
+        </is>
+      </c>
+      <c r="F198" s="9" t="inlineStr"/>
+      <c r="G198" s="9" t="inlineStr">
+        <is>
+          <t>매 xlsx_to_raw_csv.py 실행 시작 시 자동 실행. 구버전 이력 파일(임직원_직무이력('18.5월_이전).xlsx, 헤더 2행)에서 직종/직군/주직무여부 컬럼 삭제 + '직무 프로필'→'직무' 개명. 신규 '내 리포트 *.xlsx'(헤더 6행)에서는 ID 컬럼 삭제. 구버전을 신규 파일의 컬럼셋에 reindex(fill_value='')로 맞춘 뒤 concat(신규 먼저, 구버전 뒤) → 사번 기준 정렬 → '&lt;신규파일명&gt;_병합.xlsx'로 저장(원본 덮어쓰지 않음). process_job_profile.py는 이 병합 산출물만 읽는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="45" customHeight="1">
+      <c r="A199" s="8" t="n"/>
+      <c r="B199" s="9" t="n"/>
+      <c r="C199" s="9" t="n"/>
+      <c r="D199" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E199" s="9" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="F199" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G199" s="9" t="inlineStr">
+        <is>
+          <t>norm_id().</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="45" customHeight="1">
+      <c r="A200" s="8" t="n"/>
+      <c r="B200" s="9" t="n"/>
+      <c r="C200" s="9" t="n"/>
+      <c r="D200" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E200" s="9" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="F200" s="9" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="G200" s="9" t="inlineStr">
+        <is>
+          <t>clean_str() — 동일 researcher_id의 첫 값만 채택(이후 값은 무시).</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="45" customHeight="1">
+      <c r="A201" s="8" t="n"/>
+      <c r="B201" s="9" t="n"/>
+      <c r="C201" s="9" t="n"/>
+      <c r="D201" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E201" s="9" t="inlineStr">
+        <is>
+          <t>직무</t>
+        </is>
+      </c>
+      <c r="F201" s="9" t="inlineStr">
+        <is>
+          <t>job_profile_name_{i}</t>
+        </is>
+      </c>
+      <c r="G201" s="9" t="inlineStr">
+        <is>
+          <t>clean_str() — {i} 슬롯 번호는 아래 파생 규칙 참고.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="45" customHeight="1">
+      <c r="A202" s="8" t="n"/>
+      <c r="B202" s="9" t="n"/>
+      <c r="C202" s="9" t="n"/>
+      <c r="D202" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E202" s="9" t="inlineStr">
+        <is>
+          <t>시작일</t>
+        </is>
+      </c>
+      <c r="F202" s="9" t="inlineStr">
+        <is>
+          <t>job_start_date_{i}</t>
+        </is>
+      </c>
+      <c r="G202" s="9" t="inlineStr">
+        <is>
+          <t>_parse_date()(pd.Timestamp 경유) → YYYY-MM-DD. 파싱 실패 행은 그 행 자체를 제거(공란 처리 아님).</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="45" customHeight="1">
+      <c r="A203" s="8" t="n"/>
+      <c r="B203" s="9" t="n"/>
+      <c r="C203" s="9" t="n"/>
+      <c r="D203" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E203" s="9" t="inlineStr">
+        <is>
+          <t>종료일</t>
+        </is>
+      </c>
+      <c r="F203" s="9" t="inlineStr">
+        <is>
+          <t>job_end_date_{i}</t>
+        </is>
+      </c>
+      <c r="G203" s="9" t="inlineStr">
+        <is>
+          <t>_parse_date(); 종료&lt;시작이면 시작일로 보정. 공란/파싱실패는 공란 그대로(진행중 의미, '현재'로 채우지 않음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="45" customHeight="1">
+      <c r="A204" s="8" t="n"/>
+      <c r="B204" s="9" t="n"/>
+      <c r="C204" s="9" t="n"/>
+      <c r="D204" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E204" s="9" t="inlineStr">
+        <is>
+          <t>(그룹화+병합+wide 변환)</t>
+        </is>
+      </c>
+      <c r="F204" s="9" t="inlineStr">
+        <is>
+          <t>job_profile_name_i / job_start_date_i / job_end_date_i (i=1..N)</t>
+        </is>
+      </c>
+      <c r="G204" s="9" t="inlineStr">
+        <is>
+          <t>연구원별로 시작일 정렬 후, 이전 종료일+1일=다음 시작일이면 같은 직무의 연속 구간으로 병합(_merge_consecutive). 병합된 구간들을 1..N 슬롯으로 wide 전개 — N은 이번 실행 데이터에서 가장 많은 구간을 가진 사람 기준으로 가변.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="45" customHeight="1">
+      <c r="A205" s="8" t="n"/>
+      <c r="B205" s="9" t="n"/>
+      <c r="C205" s="9" t="n"/>
+      <c r="D205" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E205" s="9" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F205" s="9" t="inlineStr">
+        <is>
+          <t>valid_year, valid_month</t>
+        </is>
+      </c>
+      <c r="G205" s="9" t="inlineStr">
+        <is>
+          <t>valid_date 인자(기본 오늘)에서 계산 — write_merged_with_valid_period()의 시점보호 판정에 사용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="45" customHeight="1">
+      <c r="A206" s="8" t="n"/>
+      <c r="B206" s="9" t="n"/>
+      <c r="C206" s="9" t="n"/>
+      <c r="D206" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E206" s="9" t="inlineStr"/>
+      <c r="F206" s="9" t="inlineStr"/>
+      <c r="G206" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id 빈 행 제거. 시작일 파싱 실패 행 제거.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="45" customHeight="1">
+      <c r="A207" s="8" t="n"/>
+      <c r="B207" s="9" t="n"/>
+      <c r="C207" s="9" t="n"/>
+      <c r="D207" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E207" s="9" t="inlineStr"/>
+      <c r="F207" s="9" t="inlineStr"/>
+      <c r="G207" s="9" t="inlineStr">
+        <is>
+          <t>같은 (researcher_id,직무) 연속 구간 병합(위 파생 참고) — 대표적 dedup/병합 규칙.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="45" customHeight="1">
+      <c r="A208" s="8" t="n"/>
+      <c r="B208" s="9" t="n"/>
+      <c r="C208" s="9" t="n"/>
+      <c r="D208" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E208" s="9" t="inlineStr"/>
+      <c r="F208" s="9" t="inlineStr"/>
+      <c r="G208" s="9" t="inlineStr">
+        <is>
+          <t>write_merged_with_valid_period(): 이번 valid_year/month가 기존 저장값보다 과거면 그 사람 행 갱신 안 함(기존 유지), job_profile_history.csv에는 항상 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="20" customHeight="1">
+      <c r="A209" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B209" s="19" t="inlineStr">
+        <is>
+          <t>업무목표(24/25/26)</t>
+        </is>
+      </c>
+      <c r="C209" s="19" t="inlineStr">
+        <is>
+          <t>process_work_objective.py</t>
+        </is>
+      </c>
+      <c r="D209" s="19" t="n"/>
+      <c r="E209" s="19" t="n"/>
+      <c r="F209" s="19" t="n"/>
+      <c r="G209" s="19" t="n"/>
+    </row>
+    <row r="210" ht="45" customHeight="1">
+      <c r="A210" s="8" t="n"/>
+      <c r="B210" s="9" t="n"/>
+      <c r="C210" s="9" t="n"/>
+      <c r="D210" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E210" s="9" t="inlineStr">
+        <is>
+          <t>(연도 자체가 계산값)</t>
+        </is>
+      </c>
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>target_years()</t>
+        </is>
+      </c>
+      <c r="G210" s="9" t="inlineStr">
+        <is>
+          <t>services.evaluations.current_fiscal_year(오늘)로 회계연도(3월 시작) FY를 구해 [FY-2,FY-1,FY] 3개 연도를 매 실행마다 새로 계산 — 예: 2026-09 실행 시 FY=2026→[2024,2025,2026], 2027-03부터는 [2025,2026,2027]. 파일명은 f'업무목표{y%100:02d}.xlsx'(2자리 접미사)로 그대로 유지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="45" customHeight="1">
+      <c r="A211" s="8" t="n"/>
+      <c r="B211" s="9" t="n"/>
+      <c r="C211" s="9" t="n"/>
+      <c r="D211" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E211" s="9" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="F211" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G211" s="9" t="inlineStr">
+        <is>
+          <t>norm_id(); 빈 값 제거. (과거 이슈: 부서장 자신의 사번이 같은 헤더명 '사번'으로 혼재해 혼동을 줬으나, 원본 파일 자체에서 그 컬럼을 '부서장사번'으로 개명해 해결됨.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="45" customHeight="1">
+      <c r="A212" s="8" t="n"/>
+      <c r="B212" s="9" t="n"/>
+      <c r="C212" s="9" t="n"/>
+      <c r="D212" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E212" s="9" t="inlineStr">
+        <is>
+          <t>목표명</t>
+        </is>
+      </c>
+      <c r="F212" s="9" t="inlineStr">
+        <is>
+          <t>work_objective{연도} (조합의 절반)</t>
+        </is>
+      </c>
+      <c r="G212" s="9" t="inlineStr">
+        <is>
+          <t>아래 파생 규칙 참고.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="45" customHeight="1">
+      <c r="A213" s="8" t="n"/>
+      <c r="B213" s="9" t="n"/>
+      <c r="C213" s="9" t="n"/>
+      <c r="D213" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E213" s="9" t="inlineStr">
+        <is>
+          <t>상세설명</t>
+        </is>
+      </c>
+      <c r="F213" s="9" t="inlineStr">
+        <is>
+          <t>work_objective{연도} (조합의 절반)</t>
+        </is>
+      </c>
+      <c r="G213" s="9" t="inlineStr">
+        <is>
+          <t>아래 파생 규칙 참고.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="45" customHeight="1">
+      <c r="A214" s="8" t="n"/>
+      <c r="B214" s="9" t="n"/>
+      <c r="C214" s="9" t="n"/>
+      <c r="D214" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E214" s="9" t="inlineStr">
+        <is>
+          <t>(2개 컬럼 조합)</t>
+        </is>
+      </c>
+      <c r="F214" s="9" t="inlineStr">
+        <is>
+          <t>work_objective{4자리 연도} (예: work_objective2024)</t>
+        </is>
+      </c>
+      <c r="G214" s="9" t="inlineStr">
+        <is>
+          <t>_combine_row(목표명,상세설명): 둘 다 있으면 '- {목표명} - {상세설명}', 하나만 있으면 '- {값}', 둘 다 없으면 그 행 제외. 같은 연구원이 그 해 여러 목표(여러 행)를 썼으면 줄바꿈(\n)으로 합쳐 1개 셀로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="45" customHeight="1">
+      <c r="A215" s="8" t="n"/>
+      <c r="B215" s="9" t="n"/>
+      <c r="C215" s="9" t="n"/>
+      <c r="D215" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E215" s="9" t="inlineStr">
+        <is>
+          <t>(연도별 3개 df outer-merge)</t>
+        </is>
+      </c>
+      <c r="F215" s="9" t="inlineStr">
+        <is>
+          <t>(위와 동일 컬럼)</t>
+        </is>
+      </c>
+      <c r="G215" s="9" t="inlineStr">
+        <is>
+          <t>3개 연도 결과를 researcher_id로 outer-merge. 이번 실행에 그 연도 파일이 없거나 그 사람 데이터가 없으면, 디스크에 이미 저장된 work_objective.csv 값을 그대로 보존(진짜 처음 보는 값만 공란).</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="45" customHeight="1">
+      <c r="A216" s="8" t="n"/>
+      <c r="B216" s="9" t="n"/>
+      <c r="C216" s="9" t="n"/>
+      <c r="D216" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E216" s="9" t="inlineStr">
+        <is>
+          <t>(레거시 컬럼 자동 이관)</t>
+        </is>
+      </c>
+      <c r="F216" s="9" t="inlineStr">
+        <is>
+          <t>work_objective24→work_objective2024 등</t>
+        </is>
+      </c>
+      <c r="G216" s="9" t="inlineStr">
+        <is>
+          <t>_migrate_legacy_columns(): 기존 저장 파일의 옛 2자리 슬롯 컬럼명을 4자리 연도명으로 자동 개명(멱등적, 이미 이관됐으면 no-op). write_merged_with_valid_period()가 out_path를 다시 읽기 전에 이 이관 결과를 먼저 파일에 반영해 신/구 스키마 혼재를 방지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="45" customHeight="1">
+      <c r="A217" s="8" t="n"/>
+      <c r="B217" s="9" t="n"/>
+      <c r="C217" s="9" t="n"/>
+      <c r="D217" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E217" s="9" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F217" s="9" t="inlineStr">
+        <is>
+          <t>valid_year, valid_month</t>
+        </is>
+      </c>
+      <c r="G217" s="9" t="inlineStr">
+        <is>
+          <t>valid_date 인자(기본 오늘)에서 계산 — target_years()의 '오늘' 기준과는 독립적.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="45" customHeight="1">
+      <c r="A218" s="8" t="n"/>
+      <c r="B218" s="9" t="n"/>
+      <c r="C218" s="9" t="n"/>
+      <c r="D218" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E218" s="9" t="inlineStr"/>
+      <c r="F218" s="9" t="inlineStr"/>
+      <c r="G218" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id 빈 행 제거.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="45" customHeight="1">
+      <c r="A219" s="8" t="n"/>
+      <c r="B219" s="9" t="n"/>
+      <c r="C219" s="9" t="n"/>
+      <c r="D219" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E219" s="9" t="inlineStr"/>
+      <c r="F219" s="9" t="inlineStr"/>
+      <c r="G219" s="9" t="inlineStr">
+        <is>
+          <t>목표명·상세설명 둘 다 공란인 행 제거. 같은 연구원의 같은 해 여러 목표 행은 dedup이 아니라 줄바꿈 합산.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="45" customHeight="1">
+      <c r="A220" s="8" t="n"/>
+      <c r="B220" s="9" t="n"/>
+      <c r="C220" s="9" t="n"/>
+      <c r="D220" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E220" s="9" t="inlineStr"/>
+      <c r="F220" s="9" t="inlineStr"/>
+      <c r="G220" s="9" t="inlineStr">
+        <is>
+          <t>write_merged_with_valid_period(): 사람×연도 단위로 과거 시점 재업로드 시 건너뜀(경고), work_objective_history.csv에는 항상 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="20" customHeight="1">
+      <c r="A221" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B221" s="19" t="inlineStr">
+        <is>
+          <t>과제참여이력</t>
+        </is>
+      </c>
+      <c r="C221" s="19" t="inlineStr">
+        <is>
+          <t>process_tasks.py</t>
+        </is>
+      </c>
+      <c r="D221" s="19" t="n"/>
+      <c r="E221" s="19" t="n"/>
+      <c r="F221" s="19" t="n"/>
+      <c r="G221" s="19" t="n"/>
+    </row>
+    <row r="222" ht="45" customHeight="1">
+      <c r="A222" s="8" t="n"/>
+      <c r="B222" s="9" t="n"/>
+      <c r="C222" s="9" t="n"/>
+      <c r="D222" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E222" s="9" t="inlineStr">
+        <is>
+          <t>(원본 형식)</t>
+        </is>
+      </c>
+      <c r="F222" s="9" t="inlineStr"/>
+      <c r="G222" s="9" t="inlineStr">
+        <is>
+          <t>원본은 .xlsb(바이너리 엑셀, 개인별과제투입기간데이터_260114.xlsb) — read_xlsx()가 처리(이 스크립트 자체엔 xlsb 전용 코드 없음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="45" customHeight="1">
+      <c r="A223" s="8" t="n"/>
+      <c r="B223" s="9" t="n"/>
+      <c r="C223" s="9" t="n"/>
+      <c r="D223" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E223" s="9" t="inlineStr">
+        <is>
+          <t>KNOXID</t>
+        </is>
+      </c>
+      <c r="F223" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G223" s="9" t="inlineStr">
+        <is>
+          <t>norm_id() 8자리.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="45" customHeight="1">
+      <c r="A224" s="8" t="n"/>
+      <c r="B224" s="9" t="n"/>
+      <c r="C224" s="9" t="n"/>
+      <c r="D224" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E224" s="9" t="inlineStr">
+        <is>
+          <t>과제명</t>
+        </is>
+      </c>
+      <c r="F224" s="9" t="inlineStr">
+        <is>
+          <t>task_name</t>
+        </is>
+      </c>
+      <c r="G224" s="9" t="inlineStr">
+        <is>
+          <t>trim만 — '그 시점 시스템이 알려준 현재 이름'을 그대로 보존(보정된 이름은 the_task_name 참고).</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="45" customHeight="1">
+      <c r="A225" s="8" t="n"/>
+      <c r="B225" s="9" t="n"/>
+      <c r="C225" s="9" t="n"/>
+      <c r="D225" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E225" s="9" t="inlineStr">
+        <is>
+          <t>시작일</t>
+        </is>
+      </c>
+      <c r="F225" s="9" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="G225" s="9" t="inlineStr">
+        <is>
+          <t>parse_yyyymmdd() → YYYY-MM-DD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="45" customHeight="1">
+      <c r="A226" s="8" t="n"/>
+      <c r="B226" s="9" t="n"/>
+      <c r="C226" s="9" t="n"/>
+      <c r="D226" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E226" s="9" t="inlineStr">
+        <is>
+          <t>해제일</t>
+        </is>
+      </c>
+      <c r="F226" s="9" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="G226" s="9" t="inlineStr">
+        <is>
+          <t>parse_yyyymmdd().</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="45" customHeight="1">
+      <c r="A227" s="8" t="n"/>
+      <c r="B227" s="9" t="n"/>
+      <c r="C227" s="9" t="n"/>
+      <c r="D227" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E227" s="9" t="inlineStr">
+        <is>
+          <t>투입률</t>
+        </is>
+      </c>
+      <c r="F227" s="9" t="inlineStr">
+        <is>
+          <t>input_rate</t>
+        </is>
+      </c>
+      <c r="G227" s="9" t="inlineStr">
+        <is>
+          <t>_parse_rate(): (0.0,1.0] 범위 숫자는 비율로 보고 ×100(반올림), 아니면 그대로 반올림해 정수문자열; 파싱 실패 시 공란.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="45" customHeight="1">
+      <c r="A228" s="8" t="n"/>
+      <c r="B228" s="9" t="n"/>
+      <c r="C228" s="9" t="n"/>
+      <c r="D228" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E228" s="9" t="inlineStr">
+        <is>
+          <t>(tasks_information.csv 역조회)</t>
+        </is>
+      </c>
+      <c r="F228" s="9" t="inlineStr">
+        <is>
+          <t>task_code, the_task_name</t>
+        </is>
+      </c>
+      <c r="G228" s="9" t="inlineStr">
+        <is>
+          <t>process_task_information.py 산출물을 task_name→task_code, task_code→[(write_date,task_name),...] 개명이력으로 만든 뒤, 각 참여기간을 실제 개명 시점 기준 구간으로 쪼개(_split_by_name_history) '그 구간에 실제로 불리던 이름'을 the_task_name으로 부여 — 원본 1행이 개명 이력에 따라 여러 행으로 늘어날 수 있음. 매핑 실패/이력 없음이면 원본 task_name·빈 task_code로 폴백(정보 손실 방지).</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="45" customHeight="1">
+      <c r="A229" s="8" t="n"/>
+      <c r="B229" s="9" t="n"/>
+      <c r="C229" s="9" t="n"/>
+      <c r="D229" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E229" s="9" t="inlineStr">
+        <is>
+          <t>(연속구간 병합)</t>
+        </is>
+      </c>
+      <c r="F229" s="9" t="inlineStr">
+        <is>
+          <t>start_date/end_date/input_rate (병합 후 값)</t>
+        </is>
+      </c>
+      <c r="G229" s="9" t="inlineStr">
+        <is>
+          <t>_merge_consecutive_periods(): 같은 (researcher_id,task_name)에서 end_date==다음 start_date이거나 같은 연-월(재참여로 간주)이면 병합(가장 이른 시작/가장 늦은 종료 채택, input_rate는 더 최근 값 채택) — the_task_name 분리보다 먼저 수행.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="45" customHeight="1">
+      <c r="A230" s="8" t="n"/>
+      <c r="B230" s="9" t="n"/>
+      <c r="C230" s="9" t="n"/>
+      <c r="D230" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E230" s="9" t="inlineStr"/>
+      <c r="F230" s="9" t="inlineStr"/>
+      <c r="G230" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id 빈 행 제거.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="45" customHeight="1">
+      <c r="A231" s="8" t="n"/>
+      <c r="B231" s="9" t="n"/>
+      <c r="C231" s="9" t="n"/>
+      <c r="D231" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E231" s="9" t="inlineStr"/>
+      <c r="F231" s="9" t="inlineStr"/>
+      <c r="G231" s="9" t="inlineStr">
+        <is>
+          <t>동일 (researcher_id,task_name) 연속기간 병합(위 파생 참고, 행수 감소 가능) → 개명이력 분리(행수 다시 증가 가능).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="45" customHeight="1">
+      <c r="A232" s="8" t="n"/>
+      <c r="B232" s="9" t="n"/>
+      <c r="C232" s="9" t="n"/>
+      <c r="D232" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E232" s="9" t="inlineStr"/>
+      <c r="F232" s="9" t="inlineStr"/>
+      <c r="G232" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id, start_date 정렬 후 write_merged()(시점보호 없음) TABLE_KEYS['tasks'] upsert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="20" customHeight="1">
+      <c r="A233" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="B233" s="19" t="inlineStr">
+        <is>
+          <t>과제별컨플</t>
+        </is>
+      </c>
+      <c r="C233" s="19" t="inlineStr">
+        <is>
+          <t>process_project_confl.py</t>
+        </is>
+      </c>
+      <c r="D233" s="19" t="n"/>
+      <c r="E233" s="19" t="n"/>
+      <c r="F233" s="19" t="n"/>
+      <c r="G233" s="19" t="n"/>
+    </row>
+    <row r="234" ht="45" customHeight="1">
+      <c r="A234" s="8" t="n"/>
+      <c r="B234" s="9" t="n"/>
+      <c r="C234" s="9" t="n"/>
+      <c r="D234" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E234" s="9" t="inlineStr">
+        <is>
+          <t>소속</t>
+        </is>
+      </c>
+      <c r="F234" s="9" t="inlineStr">
+        <is>
+          <t>dep_name</t>
+        </is>
+      </c>
+      <c r="G234" s="9" t="inlineStr">
+        <is>
+          <t>clean_str()만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="45" customHeight="1">
+      <c r="A235" s="8" t="n"/>
+      <c r="B235" s="9" t="n"/>
+      <c r="C235" s="9" t="n"/>
+      <c r="D235" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E235" s="9" t="inlineStr">
+        <is>
+          <t>과제명</t>
+        </is>
+      </c>
+      <c r="F235" s="9" t="inlineStr">
+        <is>
+          <t>project_name</t>
+        </is>
+      </c>
+      <c r="G235" s="9" t="inlineStr">
+        <is>
+          <t>clean_str()만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="45" customHeight="1">
+      <c r="A236" s="8" t="n"/>
+      <c r="B236" s="9" t="n"/>
+      <c r="C236" s="9" t="n"/>
+      <c r="D236" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E236" s="9" t="inlineStr">
+        <is>
+          <t>컨플 주소</t>
+        </is>
+      </c>
+      <c r="F236" s="9" t="inlineStr">
+        <is>
+          <t>confl_address</t>
+        </is>
+      </c>
+      <c r="G236" s="9" t="inlineStr">
+        <is>
+          <t>clean_str()만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="45" customHeight="1">
+      <c r="A237" s="8" t="n"/>
+      <c r="B237" s="9" t="n"/>
+      <c r="C237" s="9" t="n"/>
+      <c r="D237" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E237" s="9" t="inlineStr"/>
+      <c r="F237" s="9" t="inlineStr"/>
+      <c r="G237" s="9" t="inlineStr">
+        <is>
+          <t>'xlsx를 CSV로 변환(추가 가공 없음)' — 순수 1:1 rename+공백정리, 파생 컬럼 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="45" customHeight="1">
+      <c r="A238" s="8" t="n"/>
+      <c r="B238" s="9" t="n"/>
+      <c r="C238" s="9" t="n"/>
+      <c r="D238" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E238" s="9" t="inlineStr"/>
+      <c r="F238" s="9" t="inlineStr"/>
+      <c r="G238" s="9" t="inlineStr">
+        <is>
+          <t>project_name 빈 행 제거. write_merged() TABLE_KEYS['project_confl_address'] upsert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="20" customHeight="1">
+      <c r="A239" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="B239" s="19" t="inlineStr">
+        <is>
+          <t>직무정보(표준)</t>
+        </is>
+      </c>
+      <c r="C239" s="19" t="inlineStr">
+        <is>
+          <t>process_job_profile_standard.py</t>
+        </is>
+      </c>
+      <c r="D239" s="19" t="n"/>
+      <c r="E239" s="19" t="n"/>
+      <c r="F239" s="19" t="n"/>
+      <c r="G239" s="19" t="n"/>
+    </row>
+    <row r="240" ht="45" customHeight="1">
+      <c r="A240" s="8" t="n"/>
+      <c r="B240" s="9" t="n"/>
+      <c r="C240" s="9" t="n"/>
+      <c r="D240" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E240" s="9" t="inlineStr">
+        <is>
+          <t>직무</t>
+        </is>
+      </c>
+      <c r="F240" s="9" t="inlineStr">
+        <is>
+          <t>job_profile_standard</t>
+        </is>
+      </c>
+      <c r="G240" s="9" t="inlineStr">
+        <is>
+          <t>clean_str()만; 비면 그 행 skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="45" customHeight="1">
+      <c r="A241" s="8" t="n"/>
+      <c r="B241" s="9" t="n"/>
+      <c r="C241" s="9" t="n"/>
+      <c r="D241" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E241" s="9" t="inlineStr">
+        <is>
+          <t>정의</t>
+        </is>
+      </c>
+      <c r="F241" s="9" t="inlineStr">
+        <is>
+          <t>explain_job_profile_standard</t>
+        </is>
+      </c>
+      <c r="G241" s="9" t="inlineStr">
+        <is>
+          <t>clean_str()만; 비어도 행 유지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="45" customHeight="1">
+      <c r="A242" s="8" t="n"/>
+      <c r="B242" s="9" t="n"/>
+      <c r="C242" s="9" t="n"/>
+      <c r="D242" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E242" s="9" t="inlineStr"/>
+      <c r="F242" s="9" t="inlineStr"/>
+      <c r="G242" s="9" t="inlineStr">
+        <is>
+          <t>직무 컬럼이 비면 행 제거. 직무/정의 헤더 둘 다 없으면 전체 중단.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="45" customHeight="1">
+      <c r="A243" s="8" t="n"/>
+      <c r="B243" s="9" t="n"/>
+      <c r="C243" s="9" t="n"/>
+      <c r="D243" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E243" s="9" t="inlineStr"/>
+      <c r="F243" s="9" t="inlineStr"/>
+      <c r="G243" s="9" t="inlineStr">
+        <is>
+          <t>JSON 배열로 매 실행마다 전체 덮어쓰기(job_profile_info_standard.json) — 업서트 없음, 다른 대부분 스크립트와 다른 유일한 순수 참조 테이블 패턴(다음 2개 항목도 동일).</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="20" customHeight="1">
+      <c r="A244" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B244" s="19" t="inlineStr">
+        <is>
+          <t>직무정보(SAIT자체)</t>
+        </is>
+      </c>
+      <c r="C244" s="19" t="inlineStr">
+        <is>
+          <t>process_job_profile_sait.py</t>
+        </is>
+      </c>
+      <c r="D244" s="19" t="n"/>
+      <c r="E244" s="19" t="n"/>
+      <c r="F244" s="19" t="n"/>
+      <c r="G244" s="19" t="n"/>
+    </row>
+    <row r="245" ht="45" customHeight="1">
+      <c r="A245" s="8" t="n"/>
+      <c r="B245" s="9" t="n"/>
+      <c r="C245" s="9" t="n"/>
+      <c r="D245" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E245" s="9" t="inlineStr">
+        <is>
+          <t>직무</t>
+        </is>
+      </c>
+      <c r="F245" s="9" t="inlineStr">
+        <is>
+          <t>job_profile_sait</t>
+        </is>
+      </c>
+      <c r="G245" s="9" t="inlineStr">
+        <is>
+          <t>clean_str()만; 비면 행 skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="45" customHeight="1">
+      <c r="A246" s="8" t="n"/>
+      <c r="B246" s="9" t="n"/>
+      <c r="C246" s="9" t="n"/>
+      <c r="D246" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E246" s="9" t="inlineStr">
+        <is>
+          <t>세부직무</t>
+        </is>
+      </c>
+      <c r="F246" s="9" t="inlineStr">
+        <is>
+          <t>job_profile_detail_sait</t>
+        </is>
+      </c>
+      <c r="G246" s="9" t="inlineStr">
+        <is>
+          <t>clean_str()만; 비어도 행 유지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="45" customHeight="1">
+      <c r="A247" s="8" t="n"/>
+      <c r="B247" s="9" t="n"/>
+      <c r="C247" s="9" t="n"/>
+      <c r="D247" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E247" s="9" t="inlineStr">
+        <is>
+          <t>정의</t>
+        </is>
+      </c>
+      <c r="F247" s="9" t="inlineStr">
+        <is>
+          <t>explain_job_profile_sait</t>
+        </is>
+      </c>
+      <c r="G247" s="9" t="inlineStr">
+        <is>
+          <t>clean_str()만; 비어도 행 유지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="45" customHeight="1">
+      <c r="A248" s="8" t="n"/>
+      <c r="B248" s="9" t="n"/>
+      <c r="C248" s="9" t="n"/>
+      <c r="D248" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E248" s="9" t="inlineStr"/>
+      <c r="F248" s="9" t="inlineStr"/>
+      <c r="G248" s="9" t="inlineStr">
+        <is>
+          <t>직무 컬럼이 비면 행 제거. 3개 헤더 모두 필수(없으면 중단).</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="45" customHeight="1">
+      <c r="A249" s="8" t="n"/>
+      <c r="B249" s="9" t="n"/>
+      <c r="C249" s="9" t="n"/>
+      <c r="D249" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E249" s="9" t="inlineStr"/>
+      <c r="F249" s="9" t="inlineStr"/>
+      <c r="G249" s="9" t="inlineStr">
+        <is>
+          <t>JSON 배열 전체 덮어쓰기(job_profile_info_sait.json) — 업서트 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="20" customHeight="1">
+      <c r="A250" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="B250" s="19" t="inlineStr">
+        <is>
+          <t>팀/리더 참조</t>
+        </is>
+      </c>
+      <c r="C250" s="19" t="inlineStr">
+        <is>
+          <t>process_team_refer.py (+ team_hierarchy.py, 관리자 화면 그리드 CRUD 병행)</t>
+        </is>
+      </c>
+      <c r="D250" s="19" t="n"/>
+      <c r="E250" s="19" t="n"/>
+      <c r="F250" s="19" t="n"/>
+      <c r="G250" s="19" t="n"/>
+    </row>
+    <row r="251" ht="45" customHeight="1">
+      <c r="A251" s="8" t="n"/>
+      <c r="B251" s="9" t="n"/>
+      <c r="C251" s="9" t="n"/>
+      <c r="D251" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E251" s="9" t="inlineStr">
+        <is>
+          <t>(인텔이크 형태)</t>
+        </is>
+      </c>
+      <c r="F251" s="9" t="inlineStr"/>
+      <c r="G251" s="9" t="inlineStr">
+        <is>
+          <t>팀참조시트.xlsx의 각 행은 '전체 경로 포함' 형태 — 자기 소속 3단계 전부를 채워서 입력(예: 3단계 소속이면 1/2/3단계부서명 전부 기재). 저장 스키마는 반대로 '자기 레벨 이름만'(own-level-only) 채우는 조직 단위 1행 구조로 team_hierarchy.derive_hierarchy()가 변환한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="45" customHeight="1">
+      <c r="A252" s="8" t="n"/>
+      <c r="B252" s="9" t="n"/>
+      <c r="C252" s="9" t="n"/>
+      <c r="D252" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E252" s="9" t="inlineStr">
+        <is>
+          <t>비공식소속부서명</t>
+        </is>
+      </c>
+      <c r="F252" s="9" t="inlineStr">
+        <is>
+          <t>org_name_wd</t>
+        </is>
+      </c>
+      <c r="G252" s="9" t="inlineStr">
+        <is>
+          <t>clean_str() — researchers.csv의 org_code와 매칭되는 핵심 키.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="45" customHeight="1">
+      <c r="A253" s="8" t="n"/>
+      <c r="B253" s="9" t="n"/>
+      <c r="C253" s="9" t="n"/>
+      <c r="D253" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E253" s="9" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="F253" s="9" t="inlineStr">
+        <is>
+          <t>work_type</t>
+        </is>
+      </c>
+      <c r="G253" s="9" t="inlineStr">
+        <is>
+          <t>clean_str() — 관리자 화면에서 R&amp;D/R&amp;D_Support/Staff 드롭다운으로 제한 입력. 공란이면 derive_hierarchy()가 'R&amp;D'로 기본 채움.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="45" customHeight="1">
+      <c r="A254" s="8" t="n"/>
+      <c r="B254" s="9" t="n"/>
+      <c r="C254" s="9" t="n"/>
+      <c r="D254" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E254" s="9" t="inlineStr">
+        <is>
+          <t>1단계부서명</t>
+        </is>
+      </c>
+      <c r="F254" s="9" t="inlineStr">
+        <is>
+          <t>dep_1st_name</t>
+        </is>
+      </c>
+      <c r="G254" s="9" t="inlineStr">
+        <is>
+          <t>clean_str() 후 태그 제거(아래 규칙 참고).</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="45" customHeight="1">
+      <c r="A255" s="8" t="n"/>
+      <c r="B255" s="9" t="n"/>
+      <c r="C255" s="9" t="n"/>
+      <c r="D255" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E255" s="9" t="inlineStr">
+        <is>
+          <t>2단계부서명</t>
+        </is>
+      </c>
+      <c r="F255" s="9" t="inlineStr">
+        <is>
+          <t>dep_2nd_name</t>
+        </is>
+      </c>
+      <c r="G255" s="9" t="inlineStr">
+        <is>
+          <t>clean_str() 후 태그 제거.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="45" customHeight="1">
+      <c r="A256" s="8" t="n"/>
+      <c r="B256" s="9" t="n"/>
+      <c r="C256" s="9" t="n"/>
+      <c r="D256" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E256" s="9" t="inlineStr">
+        <is>
+          <t>3단계부서명</t>
+        </is>
+      </c>
+      <c r="F256" s="9" t="inlineStr">
+        <is>
+          <t>dep_3rd_name</t>
+        </is>
+      </c>
+      <c r="G256" s="9" t="inlineStr">
+        <is>
+          <t>clean_str() 후 태그 제거.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="45" customHeight="1">
+      <c r="A257" s="8" t="n"/>
+      <c r="B257" s="9" t="n"/>
+      <c r="C257" s="9" t="n"/>
+      <c r="D257" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E257" s="9" t="inlineStr">
+        <is>
+          <t>조직코드</t>
+        </is>
+      </c>
+      <c r="F257" s="9" t="inlineStr">
+        <is>
+          <t>dep_code</t>
+        </is>
+      </c>
+      <c r="G257" s="9" t="inlineStr">
+        <is>
+          <t>clean_str() — 형제 조직 간 표시 순서(사내 규정), 공란이면 처음 등장 순서로 기본 채움.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="45" customHeight="1">
+      <c r="A258" s="8" t="n"/>
+      <c r="B258" s="9" t="n"/>
+      <c r="C258" s="9" t="n"/>
+      <c r="D258" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E258" s="9" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="F258" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G258" s="9" t="inlineStr">
+        <is>
+          <t>norm_id() — 조직장급만 채워짐(전체 인원 대상 아님).</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="45" customHeight="1">
+      <c r="A259" s="8" t="n"/>
+      <c r="B259" s="9" t="n"/>
+      <c r="C259" s="9" t="n"/>
+      <c r="D259" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E259" s="9" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="F259" s="9" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="G259" s="9" t="inlineStr">
+        <is>
+          <t>clean_str().</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="45" customHeight="1">
+      <c r="A260" s="8" t="n"/>
+      <c r="B260" s="9" t="n"/>
+      <c r="C260" s="9" t="n"/>
+      <c r="D260" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E260" s="9" t="inlineStr">
+        <is>
+          <t>직책</t>
+        </is>
+      </c>
+      <c r="F260" s="9" t="inlineStr">
+        <is>
+          <t>assignment_name</t>
+        </is>
+      </c>
+      <c r="G260" s="9" t="inlineStr">
+        <is>
+          <t>clean_str().</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="45" customHeight="1">
+      <c r="A261" s="8" t="n"/>
+      <c r="B261" s="9" t="n"/>
+      <c r="C261" s="9" t="n"/>
+      <c r="D261" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E261" s="9" t="inlineStr">
+        <is>
+          <t>(1/2/3단계부서명 텍스트 경로 → md5 해시)</t>
+        </is>
+      </c>
+      <c r="F261" s="9" t="inlineStr">
+        <is>
+          <t>dep_id</t>
+        </is>
+      </c>
+      <c r="G261" s="9" t="inlineStr">
+        <is>
+          <t>team_hierarchy._slug(경로): 'AUTO-{md5(경로)[:10]}' 형태로 결정적 계산 — 사람이 입력하지 않음. 조직 이름이 바뀌면 새 dep_id가 되며, '같은 조직'이라는 연속성을 굳이 유지하지 않아도 안전하다는 전제(사용자 확정, 2026-09-11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="45" customHeight="1">
+      <c r="A262" s="8" t="n"/>
+      <c r="B262" s="9" t="n"/>
+      <c r="C262" s="9" t="n"/>
+      <c r="D262" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E262" s="9" t="inlineStr">
+        <is>
+          <t>(경로의 부모 접두사)</t>
+        </is>
+      </c>
+      <c r="F262" s="9" t="inlineStr">
+        <is>
+          <t>upper_dep_id</t>
+        </is>
+      </c>
+      <c r="G262" s="9" t="inlineStr">
+        <is>
+          <t>own_path의 부모 경로에 대해 동일한 md5 슬러그 계산 — 조직도 트리(부모-자식) 구조의 근간.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="45" customHeight="1">
+      <c r="A263" s="8" t="n"/>
+      <c r="B263" s="9" t="n"/>
+      <c r="C263" s="9" t="n"/>
+      <c r="D263" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E263" s="9" t="inlineStr">
+        <is>
+          <t>(경로 길이)</t>
+        </is>
+      </c>
+      <c r="F263" s="9" t="inlineStr">
+        <is>
+          <t>team_layer</t>
+        </is>
+      </c>
+      <c r="G263" s="9" t="inlineStr">
+        <is>
+          <t>그 조직 경로의 깊이(1/2/3) 그대로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="45" customHeight="1">
+      <c r="A264" s="8" t="n"/>
+      <c r="B264" s="9" t="n"/>
+      <c r="C264" s="9" t="n"/>
+      <c r="D264" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E264" s="9" t="inlineStr">
+        <is>
+          <t>('(SAIT)'/'(기술원)' 태그 제거)</t>
+        </is>
+      </c>
+      <c r="F264" s="9" t="inlineStr">
+        <is>
+          <t>1/2/3단계부서명 (정제 후 값)</t>
+        </is>
+      </c>
+      <c r="G264" s="9" t="inlineStr">
+        <is>
+          <t>같은 조직이 관점에 따라 '...(SAIT)'/'...(기술원)'로 다르게 표기되는 경우를 정규식으로 태그만 지워 하나로 합침(2026-09-15) — 이 결과 여러 원본 표기가 같은 dep_id로 합쳐지면 저장 시 '병합 확인' 경고를 관리자 화면에 표시.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="45" customHeight="1">
+      <c r="A265" s="8" t="n"/>
+      <c r="B265" s="9" t="n"/>
+      <c r="C265" s="9" t="n"/>
+      <c r="D265" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E265" s="9" t="inlineStr">
+        <is>
+          <t>(이번 저장에 없는 살아있는 dep_id)</t>
+        </is>
+      </c>
+      <c r="F265" s="9" t="inlineStr">
+        <is>
+          <t>deleted=Y (톰스톤)</t>
+        </is>
+      </c>
+      <c r="G265" s="9" t="inlineStr">
+        <is>
+          <t>tombstone_missing_dep_ids(): xlsx 일괄 업로드/그리드 저장 모두 '이번 제출=조직 전체'로 간주해, 이번에 없는 기존 dep_id는 실제 삭제 대신 deleted='Y' 신규 날짜 행으로 표시(이력은 남기되 '현재' 판정에서만 제외).</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="45" customHeight="1">
+      <c r="A266" s="8" t="n"/>
+      <c r="B266" s="9" t="n"/>
+      <c r="C266" s="9" t="n"/>
+      <c r="D266" s="21" t="inlineStr">
+        <is>
+          <t>파생</t>
+        </is>
+      </c>
+      <c r="E266" s="9" t="inlineStr">
+        <is>
+          <t>(같은 org_name_wd의 과거 값 승계)</t>
+        </is>
+      </c>
+      <c r="F266" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id/name/assignment_name (신규 업로드분)</t>
+        </is>
+      </c>
+      <c r="G266" s="9" t="inlineStr">
+        <is>
+          <t>_backfill_leader_fields(): 새 업로드에 이 값들이 비어 있으면, 같은 비공식소속부서명(org_name_wd)의 '현재' 저장값으로 채운다 — 단 이번 valid_date가 그 조직의 기존 저장 시점보다 같거나 미래일 때만(과거 시점 소급 입력에는 적용 안 함). 그리드 저장(save_snapshot)에는 적용하지 않음(관리자가 의도적으로 공란 처리할 수 있어야 하므로).</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="45" customHeight="1">
+      <c r="A267" s="8" t="n"/>
+      <c r="B267" s="9" t="n"/>
+      <c r="C267" s="9" t="n"/>
+      <c r="D267" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E267" s="9" t="inlineStr"/>
+      <c r="F267" s="9" t="inlineStr"/>
+      <c r="G267" s="9" t="inlineStr">
+        <is>
+          <t>1단계부서명이 완전히 빈 행은 저장에서 제외(관리자 그리드 저장 시 필터링).</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="45" customHeight="1">
+      <c r="A268" s="8" t="n"/>
+      <c r="B268" s="9" t="n"/>
+      <c r="C268" s="9" t="n"/>
+      <c r="D268" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E268" s="9" t="inlineStr"/>
+      <c r="F268" s="9" t="inlineStr"/>
+      <c r="G268" s="9" t="inlineStr">
+        <is>
+          <t>자연키 (dep_id, valid_year, valid_month, valid_day) — 시점 포함 4중키로 누적. 같은 날짜 안에서 같은 dep_id가 중복되면(예: 그리드에서 실수로 두 번 추가) find_duplicate_dep_ids()가 경고.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="45" customHeight="1">
+      <c r="A269" s="8" t="n"/>
+      <c r="B269" s="9" t="n"/>
+      <c r="C269" s="9" t="n"/>
+      <c r="D269" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E269" s="9" t="inlineStr"/>
+      <c r="F269" s="9" t="inlineStr"/>
+      <c r="G269" s="9" t="inlineStr">
+        <is>
+          <t>read_team_refer() 조회 시 dep_id별로 '현재/특정 시점 이하 최신' 1개 스냅샷만 골라 반환(deleted='Y'인 최신 스냅샷은 그 dep_id를 제외) — 조직도·부서 필터·기간(과거포함) 조회가 모두 이 함수를 공유.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="20" customHeight="1">
+      <c r="A270" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="B270" s="19" t="inlineStr">
+        <is>
+          <t>어학</t>
+        </is>
+      </c>
+      <c r="C270" s="19" t="inlineStr">
+        <is>
+          <t>process_language_qualification.py</t>
+        </is>
+      </c>
+      <c r="D270" s="19" t="n"/>
+      <c r="E270" s="19" t="n"/>
+      <c r="F270" s="19" t="n"/>
+      <c r="G270" s="19" t="n"/>
+    </row>
+    <row r="271" ht="45" customHeight="1">
+      <c r="A271" s="8" t="n"/>
+      <c r="B271" s="9" t="n"/>
+      <c r="C271" s="9" t="n"/>
+      <c r="D271" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E271" s="9" t="inlineStr">
+        <is>
+          <t>(원본 레이아웃)</t>
+        </is>
+      </c>
+      <c r="F271" s="9" t="inlineStr"/>
+      <c r="G271" s="9" t="inlineStr">
+        <is>
+          <t>A열=사번, B~Y열은 무관, Z열부터 언어별로 6컬럼 반복 블록: '[{언어} 회화]', 발급일, 만료일, '[{언어} 필기]', 발급일, 만료일 ... (2026-09-03 정정: 대괄호로 감싼 표기임을 확인). 헤더는 실제 7번째 행(1~6행 무시, 사용자 확인).</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="45" customHeight="1">
+      <c r="A272" s="8" t="n"/>
+      <c r="B272" s="9" t="n"/>
+      <c r="C272" s="9" t="n"/>
+      <c r="D272" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E272" s="9" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="F272" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G272" s="9" t="inlineStr">
+        <is>
+          <t>norm_id().</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="45" customHeight="1">
+      <c r="A273" s="8" t="n"/>
+      <c r="B273" s="9" t="n"/>
+      <c r="C273" s="9" t="n"/>
+      <c r="D273" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E273" s="9" t="inlineStr">
+        <is>
+          <t>'[{언어} 회화]' (헤더 자체, 정규식 ^\[(.+?)\s*회화\]$)</t>
+        </is>
+      </c>
+      <c r="F273" s="9" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="G273" s="9" t="inlineStr">
+        <is>
+          <t>셀 값이 아니라 헤더 문자열에서 대괄호+'회화' 제거한 언어명만 추출(예: '[영어 회화]'→'영어').</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="45" customHeight="1">
+      <c r="A274" s="8" t="n"/>
+      <c r="B274" s="9" t="n"/>
+      <c r="C274" s="9" t="n"/>
+      <c r="D274" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E274" s="9" t="inlineStr">
+        <is>
+          <t>'[{언어} 회화]' (동일 컬럼의 셀 값)</t>
+        </is>
+      </c>
+      <c r="F274" s="9" t="inlineStr">
+        <is>
+          <t>speak_grade</t>
+        </is>
+      </c>
+      <c r="G274" s="9" t="inlineStr">
+        <is>
+          <t>clean_str()만 — 원본 값 그대로(예: '2등급', 등급 표기가 이미 값에 포함돼 있음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="45" customHeight="1">
+      <c r="A275" s="8" t="n"/>
+      <c r="B275" s="9" t="n"/>
+      <c r="C275" s="9" t="n"/>
+      <c r="D275" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E275" s="9" t="inlineStr">
+        <is>
+          <t>(이름이 아니라 위치로 결정 — 회화 컬럼 인덱스+2)</t>
+        </is>
+      </c>
+      <c r="F275" s="9" t="inlineStr">
+        <is>
+          <t>expiration_date</t>
+        </is>
+      </c>
+      <c r="G275" s="9" t="inlineStr">
+        <is>
+          <t>parse_flexible_date() 적용. '발급일'/'만료일' 헤더명 자체는 모든 언어 블록에서 동일해 이름만으론 구분 불가 → 컬럼 위치 오프셋(+2)으로 특정. 그 위치 헤더가 '만료일'로 시작 안 하면 WARN만 남기고 그래도 그 위치 값을 사용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="45" customHeight="1">
+      <c r="A276" s="8" t="n"/>
+      <c r="B276" s="9" t="n"/>
+      <c r="C276" s="9" t="n"/>
+      <c r="D276" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E276" s="9" t="inlineStr">
+        <is>
+          <t>(사용 안 함)</t>
+        </is>
+      </c>
+      <c r="F276" s="9" t="inlineStr"/>
+      <c r="G276" s="9" t="inlineStr">
+        <is>
+          <t>'[{언어} 필기]' 및 그 발급일/만료일 컬럼, B~Y열은 전혀 읽지 않음(사용자 확정).</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="45" customHeight="1">
+      <c r="A277" s="8" t="n"/>
+      <c r="B277" s="9" t="n"/>
+      <c r="C277" s="9" t="n"/>
+      <c r="D277" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E277" s="9" t="inlineStr"/>
+      <c r="F277" s="9" t="inlineStr"/>
+      <c r="G277" s="9" t="inlineStr">
+        <is>
+          <t>사번 공란 또는 speak_grade 공란인 행 제거(둘 다 있어야 유지).</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="45" customHeight="1">
+      <c r="A278" s="8" t="n"/>
+      <c r="B278" s="9" t="n"/>
+      <c r="C278" s="9" t="n"/>
+      <c r="D278" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E278" s="9" t="inlineStr"/>
+      <c r="F278" s="9" t="inlineStr"/>
+      <c r="G278" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id, language 정렬. **누적 안 함** — 매 실행마다 파일 전체 교체(재직자 현재값만 의미 있는 자료라는 설계, valid_year/month·이력테이블 없음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="20" customHeight="1">
+      <c r="A279" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="B279" s="19" t="inlineStr">
+        <is>
+          <t>근무 경력</t>
+        </is>
+      </c>
+      <c r="C279" s="19" t="inlineStr">
+        <is>
+          <t>process_work_experience.py</t>
+        </is>
+      </c>
+      <c r="D279" s="19" t="n"/>
+      <c r="E279" s="19" t="n"/>
+      <c r="F279" s="19" t="n"/>
+      <c r="G279" s="19" t="n"/>
+    </row>
+    <row r="280" ht="45" customHeight="1">
+      <c r="A280" s="8" t="n"/>
+      <c r="B280" s="9" t="n"/>
+      <c r="C280" s="9" t="n"/>
+      <c r="D280" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E280" s="9" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="F280" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G280" s="9" t="inlineStr">
+        <is>
+          <t>norm_id(); 빈 값 제거. 필수(없으면 중단).</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="45" customHeight="1">
+      <c r="A281" s="8" t="n"/>
+      <c r="B281" s="9" t="n"/>
+      <c r="C281" s="9" t="n"/>
+      <c r="D281" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E281" s="9" t="inlineStr">
+        <is>
+          <t>회사</t>
+        </is>
+      </c>
+      <c r="F281" s="9" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="G281" s="9" t="inlineStr">
+        <is>
+          <t>trim만(컬럼 없으면 전부 공란).</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="45" customHeight="1">
+      <c r="A282" s="8" t="n"/>
+      <c r="B282" s="9" t="n"/>
+      <c r="C282" s="9" t="n"/>
+      <c r="D282" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E282" s="9" t="inlineStr">
+        <is>
+          <t>시작일</t>
+        </is>
+      </c>
+      <c r="F282" s="9" t="inlineStr">
+        <is>
+          <t>work_start_date</t>
+        </is>
+      </c>
+      <c r="G282" s="9" t="inlineStr">
+        <is>
+          <t>parse_flexible_date() → YYYY-MM-DD(컬럼 없으면 공란).</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="45" customHeight="1">
+      <c r="A283" s="8" t="n"/>
+      <c r="B283" s="9" t="n"/>
+      <c r="C283" s="9" t="n"/>
+      <c r="D283" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E283" s="9" t="inlineStr">
+        <is>
+          <t>종료일</t>
+        </is>
+      </c>
+      <c r="F283" s="9" t="inlineStr">
+        <is>
+          <t>work_end_date</t>
+        </is>
+      </c>
+      <c r="G283" s="9" t="inlineStr">
+        <is>
+          <t>parse_flexible_date(); 컬럼 없거나 셀이 비면 공란 그대로 — '현재'/재직중으로 채우지 않음(사용자 확정).</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="45" customHeight="1">
+      <c r="A284" s="8" t="n"/>
+      <c r="B284" s="9" t="n"/>
+      <c r="C284" s="9" t="n"/>
+      <c r="D284" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E284" s="9" t="inlineStr">
+        <is>
+          <t>직무명</t>
+        </is>
+      </c>
+      <c r="F284" s="9" t="inlineStr">
+        <is>
+          <t>role_name</t>
+        </is>
+      </c>
+      <c r="G284" s="9" t="inlineStr">
+        <is>
+          <t>trim만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="45" customHeight="1">
+      <c r="A285" s="8" t="n"/>
+      <c r="B285" s="9" t="n"/>
+      <c r="C285" s="9" t="n"/>
+      <c r="D285" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E285" s="9" t="inlineStr"/>
+      <c r="F285" s="9" t="inlineStr"/>
+      <c r="G285" s="9" t="inlineStr">
+        <is>
+          <t>사번 공란 행 제거.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="45" customHeight="1">
+      <c r="A286" s="8" t="n"/>
+      <c r="B286" s="9" t="n"/>
+      <c r="C286" s="9" t="n"/>
+      <c r="D286" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E286" s="9" t="inlineStr"/>
+      <c r="F286" s="9" t="inlineStr"/>
+      <c r="G286" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id 오름차순, work_start_date 내림차순 정렬(정렬만, 필터 아님).</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="45" customHeight="1">
+      <c r="A287" s="8" t="n"/>
+      <c r="B287" s="9" t="n"/>
+      <c r="C287" s="9" t="n"/>
+      <c r="D287" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E287" s="9" t="inlineStr"/>
+      <c r="F287" s="9" t="inlineStr"/>
+      <c r="G287" s="9" t="inlineStr">
+        <is>
+          <t>**2026-09-02부터 자연키 upsert로 전환**(원래는 researcher_id 단위 그룹 교체) — 자연키=(researcher_id,company_name,work_start_date). 같은 키는 정정, 다른 키는 누적, 이번 업로드에 없는 사람(전배·퇴직 등)의 기존 경력은 삭제되지 않고 보존됨. 변경 사유: 본인 경력은 소급 수정이 거의 없고, 그룹 교체 방식은 그 사람이 이번 파일에서 빠졌을 때(전배 등) 기존 이력이 사라질 위험이 있었기 때문.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="20" customHeight="1">
+      <c r="A288" s="18" t="n">
+        <v>24</v>
+      </c>
+      <c r="B288" s="19" t="inlineStr">
+        <is>
+          <t>기술이전</t>
+        </is>
+      </c>
+      <c r="C288" s="19" t="inlineStr">
+        <is>
+          <t>(전용 처리기 없음 — 원본 통과)</t>
+        </is>
+      </c>
+      <c r="D288" s="19" t="n"/>
+      <c r="E288" s="19" t="n"/>
+      <c r="F288" s="19" t="n"/>
+      <c r="G288" s="19" t="n"/>
+    </row>
+    <row r="289" ht="45" customHeight="1">
+      <c r="A289" s="8" t="n"/>
+      <c r="B289" s="9" t="n"/>
+      <c r="C289" s="9" t="n"/>
+      <c r="D289" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E289" s="9" t="inlineStr"/>
+      <c r="F289" s="9" t="inlineStr"/>
+      <c r="G289" s="9" t="inlineStr">
+        <is>
+          <t>technology_transfer_raw.xlsx의 컬럼명을 그대로 최종 스키마로 사용 — run_pipeline.py의 범용 raw-passthrough 경로(TABLE_KEYS에 등록된 자연키가 실제 컬럼에 있으면 업서트, 없으면 전체 교체로 안전 폴백). 별도 헤더 매핑/변환 코드 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="20" customHeight="1">
+      <c r="A290" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="B290" s="19" t="inlineStr">
+        <is>
+          <t>파견이력</t>
+        </is>
+      </c>
+      <c r="C290" s="19" t="inlineStr">
+        <is>
+          <t>(전용 처리기 없음 — 원본 통과)</t>
+        </is>
+      </c>
+      <c r="D290" s="19" t="n"/>
+      <c r="E290" s="19" t="n"/>
+      <c r="F290" s="19" t="n"/>
+      <c r="G290" s="19" t="n"/>
+    </row>
+    <row r="291" ht="45" customHeight="1">
+      <c r="A291" s="8" t="n"/>
+      <c r="B291" s="9" t="n"/>
+      <c r="C291" s="9" t="n"/>
+      <c r="D291" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E291" s="9" t="inlineStr"/>
+      <c r="F291" s="9" t="inlineStr"/>
+      <c r="G291" s="9" t="inlineStr">
+        <is>
+          <t>transfers_raw.xlsx 컬럼 그대로 사용. 기술이전과 동일한 raw-passthrough 경로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="20" customHeight="1">
+      <c r="A292" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="B292" s="19" t="inlineStr">
+        <is>
+          <t>자격증</t>
+        </is>
+      </c>
+      <c r="C292" s="19" t="inlineStr">
+        <is>
+          <t>(전용 처리기 없음 — 원본 통과)</t>
+        </is>
+      </c>
+      <c r="D292" s="19" t="n"/>
+      <c r="E292" s="19" t="n"/>
+      <c r="F292" s="19" t="n"/>
+      <c r="G292" s="19" t="n"/>
+    </row>
+    <row r="293" ht="45" customHeight="1">
+      <c r="A293" s="8" t="n"/>
+      <c r="B293" s="9" t="n"/>
+      <c r="C293" s="9" t="n"/>
+      <c r="D293" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E293" s="9" t="inlineStr"/>
+      <c r="F293" s="9" t="inlineStr"/>
+      <c r="G293" s="9" t="inlineStr">
+        <is>
+          <t>certifications_raw.xlsx 컬럼 그대로 사용. 동일한 raw-passthrough 경로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="20" customHeight="1">
+      <c r="A294" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="B294" s="19" t="inlineStr">
+        <is>
+          <t>승계후보</t>
+        </is>
+      </c>
+      <c r="C294" s="19" t="inlineStr">
+        <is>
+          <t>(전용 처리기 없음 — 원본 통과)</t>
+        </is>
+      </c>
+      <c r="D294" s="19" t="n"/>
+      <c r="E294" s="19" t="n"/>
+      <c r="F294" s="19" t="n"/>
+      <c r="G294" s="19" t="n"/>
+    </row>
+    <row r="295" ht="45" customHeight="1">
+      <c r="A295" s="8" t="n"/>
+      <c r="B295" s="9" t="n"/>
+      <c r="C295" s="9" t="n"/>
+      <c r="D295" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E295" s="9" t="inlineStr"/>
+      <c r="F295" s="9" t="inlineStr"/>
+      <c r="G295" s="9" t="inlineStr">
+        <is>
+          <t>succession_raw.xlsx 컬럼 그대로 사용. 동일한 raw-passthrough 경로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="20" customHeight="1">
+      <c r="A296" s="18" t="n">
+        <v>28</v>
+      </c>
+      <c r="B296" s="19" t="inlineStr">
+        <is>
+          <t>직무_직군_맵핑</t>
+        </is>
+      </c>
+      <c r="C296" s="19" t="inlineStr">
+        <is>
+          <t>process_mapping_job_function.py</t>
+        </is>
+      </c>
+      <c r="D296" s="19" t="n"/>
+      <c r="E296" s="19" t="n"/>
+      <c r="F296" s="19" t="n"/>
+      <c r="G296" s="19" t="n"/>
+    </row>
+    <row r="297" ht="45" customHeight="1">
+      <c r="A297" s="8" t="n"/>
+      <c r="B297" s="9" t="n"/>
+      <c r="C297" s="9" t="n"/>
+      <c r="D297" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E297" s="9" t="inlineStr">
+        <is>
+          <t>직무</t>
+        </is>
+      </c>
+      <c r="F297" s="9" t="inlineStr">
+        <is>
+          <t>job_function</t>
+        </is>
+      </c>
+      <c r="G297" s="9" t="inlineStr">
+        <is>
+          <t>그대로 저장(가공 없음) — researchers.csv의 job_function과 텍스트 매칭되는 키.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="45" customHeight="1">
+      <c r="A298" s="8" t="n"/>
+      <c r="B298" s="9" t="n"/>
+      <c r="C298" s="9" t="n"/>
+      <c r="D298" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E298" s="9" t="inlineStr">
+        <is>
+          <t>직군(DS)</t>
+        </is>
+      </c>
+      <c r="F298" s="9" t="inlineStr">
+        <is>
+          <t>job_category_DS</t>
+        </is>
+      </c>
+      <c r="G298" s="9" t="inlineStr">
+        <is>
+          <t>그대로 저장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="45" customHeight="1">
+      <c r="A299" s="8" t="n"/>
+      <c r="B299" s="9" t="n"/>
+      <c r="C299" s="9" t="n"/>
+      <c r="D299" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E299" s="9" t="inlineStr">
+        <is>
+          <t>직군(SAIT)</t>
+        </is>
+      </c>
+      <c r="F299" s="9" t="inlineStr">
+        <is>
+          <t>job_category_SAIT</t>
+        </is>
+      </c>
+      <c r="G299" s="9" t="inlineStr">
+        <is>
+          <t>그대로 저장(exception_job_function.csv가 있으면 이 값만 override됨).</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="45" customHeight="1">
+      <c r="A300" s="8" t="n"/>
+      <c r="B300" s="9" t="n"/>
+      <c r="C300" s="9" t="n"/>
+      <c r="D300" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E300" s="9" t="inlineStr"/>
+      <c r="F300" s="9" t="inlineStr"/>
+      <c r="G300" s="9" t="inlineStr">
+        <is>
+          <t>job_function 빈 행 제거. job_function 중복 행은 첫 번째만 채택(경고) — 이후 매칭이 항상 1:1이 되도록 보장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="45" customHeight="1">
+      <c r="A301" s="8" t="n"/>
+      <c r="B301" s="9" t="n"/>
+      <c r="C301" s="9" t="n"/>
+      <c r="D301" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E301" s="9" t="inlineStr"/>
+      <c r="F301" s="9" t="inlineStr"/>
+      <c r="G301" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id 개념 없는 순수 참조 테이블 — 매 실행마다 파일 전체 새로 작성(업서트 아님).</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="20" customHeight="1">
+      <c r="A302" s="18" t="n">
+        <v>29</v>
+      </c>
+      <c r="B302" s="19" t="inlineStr">
+        <is>
+          <t>직군 예외자</t>
+        </is>
+      </c>
+      <c r="C302" s="19" t="inlineStr">
+        <is>
+          <t>process_exception_job_function.py</t>
+        </is>
+      </c>
+      <c r="D302" s="19" t="n"/>
+      <c r="E302" s="19" t="n"/>
+      <c r="F302" s="19" t="n"/>
+      <c r="G302" s="19" t="n"/>
+    </row>
+    <row r="303" ht="45" customHeight="1">
+      <c r="A303" s="8" t="n"/>
+      <c r="B303" s="9" t="n"/>
+      <c r="C303" s="9" t="n"/>
+      <c r="D303" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E303" s="9" t="inlineStr">
+        <is>
+          <t>사원번호</t>
+        </is>
+      </c>
+      <c r="F303" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G303" s="9" t="inlineStr">
+        <is>
+          <t>norm_id().</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="45" customHeight="1">
+      <c r="A304" s="8" t="n"/>
+      <c r="B304" s="9" t="n"/>
+      <c r="C304" s="9" t="n"/>
+      <c r="D304" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E304" s="9" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="F304" s="9" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="G304" s="9" t="inlineStr">
+        <is>
+          <t>그대로 저장(참고용, 매칭 키 아님).</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="45" customHeight="1">
+      <c r="A305" s="8" t="n"/>
+      <c r="B305" s="9" t="n"/>
+      <c r="C305" s="9" t="n"/>
+      <c r="D305" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E305" s="9" t="inlineStr">
+        <is>
+          <t>직군예외</t>
+        </is>
+      </c>
+      <c r="F305" s="9" t="inlineStr">
+        <is>
+          <t>exception_job_category</t>
+        </is>
+      </c>
+      <c r="G305" s="9" t="inlineStr">
+        <is>
+          <t>그대로 저장 — services/job_category.py가 mapping_job_function 매칭 결과와 무관하게 이 값으로 SAIT직군을 강제 override(DS는 그대로 유지).</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="45" customHeight="1">
+      <c r="A306" s="8" t="n"/>
+      <c r="B306" s="9" t="n"/>
+      <c r="C306" s="9" t="n"/>
+      <c r="D306" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E306" s="9" t="inlineStr"/>
+      <c r="F306" s="9" t="inlineStr"/>
+      <c r="G306" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id 빈 행 제거. 중복 사번은 첫 행만 채택(경고).</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="45" customHeight="1">
+      <c r="A307" s="8" t="n"/>
+      <c r="B307" s="9" t="n"/>
+      <c r="C307" s="9" t="n"/>
+      <c r="D307" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E307" s="9" t="inlineStr"/>
+      <c r="F307" s="9" t="inlineStr"/>
+      <c r="G307" s="9" t="inlineStr">
+        <is>
+          <t>시점 개념 없음 — 매 실행마다 파일 전체 새로 작성. 관리자 화면 그리드 CRUD(services/exception_job_function_store.py)와 동일한 team_refer.csv에 저장하지 않는 완전 별도 파일.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="20" customHeight="1">
+      <c r="A308" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="B308" s="19" t="inlineStr">
+        <is>
+          <t>평가표기 예외자</t>
+        </is>
+      </c>
+      <c r="C308" s="19" t="inlineStr">
+        <is>
+          <t>process_evaluation_exception.py</t>
+        </is>
+      </c>
+      <c r="D308" s="19" t="n"/>
+      <c r="E308" s="19" t="n"/>
+      <c r="F308" s="19" t="n"/>
+      <c r="G308" s="19" t="n"/>
+    </row>
+    <row r="309" ht="45" customHeight="1">
+      <c r="A309" s="8" t="n"/>
+      <c r="B309" s="9" t="n"/>
+      <c r="C309" s="9" t="n"/>
+      <c r="D309" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E309" s="9" t="inlineStr">
+        <is>
+          <t>사원번호</t>
+        </is>
+      </c>
+      <c r="F309" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id</t>
+        </is>
+      </c>
+      <c r="G309" s="9" t="inlineStr">
+        <is>
+          <t>norm_id().</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="45" customHeight="1">
+      <c r="A310" s="8" t="n"/>
+      <c r="B310" s="9" t="n"/>
+      <c r="C310" s="9" t="n"/>
+      <c r="D310" s="20" t="inlineStr">
+        <is>
+          <t>매핑</t>
+        </is>
+      </c>
+      <c r="E310" s="9" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="F310" s="9" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="G310" s="9" t="inlineStr">
+        <is>
+          <t>그대로 저장(참고용).</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="45" customHeight="1">
+      <c r="A311" s="8" t="n"/>
+      <c r="B311" s="9" t="n"/>
+      <c r="C311" s="9" t="n"/>
+      <c r="D311" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E311" s="9" t="inlineStr"/>
+      <c r="F311" s="9" t="inlineStr"/>
+      <c r="G311" s="9" t="inlineStr">
+        <is>
+          <t>researcher_id 빈 행 제거. 중복 사번은 첫 행만 채택(경고).</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="45" customHeight="1">
+      <c r="A312" s="8" t="n"/>
+      <c r="B312" s="9" t="n"/>
+      <c r="C312" s="9" t="n"/>
+      <c r="D312" s="22" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="E312" s="9" t="inlineStr"/>
+      <c r="F312" s="9" t="inlineStr"/>
+      <c r="G312" s="9" t="inlineStr">
+        <is>
+          <t>시점 개념 없음 — 매 실행마다 파일 전체 새로 작성. services/evaluations.py의 format_evaluation_cell()이 이 명단에 있는 사람은 연봉등급 없이도 하반기업적만 표시하는 3번째 분기를 적용(화면·A4 인쇄카드·엑셀 다운로드 '종합' 컬럼 공통, 단 엑셀의 연봉등급/업적평가 '개별 컬럼'은 원본 값 그대로 두고 이 override를 적용하지 않음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="23" t="inlineStr">
+        <is>
+          <t>※ 교차 참고 사항(여러 스크립트 공통)</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" s="24" t="inlineStr">
+        <is>
+          <t>- researcher_id 정규화(norm_id): 거의 모든 스크립트가 공유 — 사번을 8자리 zero-pad 문자열로 통일(예: 12345→'00012345', 실수 형태 '12345.0'도 처리), 빈 값이 나오면 그 행을 제거. 예외: process_leadership.py는 Knox ID→researcher_id 역조회를 쓰고, mapping_job_function/직무정보 표준·SAIT는 researcher_id 개념 자체가 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="40" customHeight="1">
+      <c r="A316" s="24" t="inlineStr">
+        <is>
+          <t>- 날짜 파서 3종 — parse_yyyymmdd(엄격, 특허/인사발령/과제정보/과제참여이력/논문), parse_flexible_date(관대, 다양한 포맷+'9999-12-31' 같은 sentinel 날짜 정규식 폴백 지원, 양성이력/시상/어학 만료일/근무경력), process_researchers.py 자체의 _parse_date(고정 포맷 리스트, pandas 미사용). 서로 다른 함수라 동작이 미묘하게 다름.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" s="24" t="inlineStr">
+        <is>
+          <t>- 누적(업서트) 방식은 테이블마다 다르다 — (1) write_merged_with_valid_period: 자연키 + 시점보호(과거 시점 재업로드가 최신 값을 되돌리지 못하게 막고, _history.csv에 모든 시도를 기록) — evaluations/core_technology/tech_ownership/job_profile/work_objective/researchers. (2) write_merged(시점보호 없음, 이력테이블 없음): patents/nurturing/awards/hr_orders/tasks_information/tasks/project_confl_address/education/incentive_selection/publications/comments/team_refer(단, team_refer는 자체적으로 valid_year/month/day를 자연키에 포함시켜 사실상 시점 누적). (3) group_replace(그룹 단위 통째 교체): leadership_comments.csv만(researcher_id+year+evaluator_group 그룹). (4) 전체 교체(누적 안 함, researcher_id 유무와 무관): 직무정보 표준/SAIT(JSON), 어학, mapping_job_function, exception_job_function, evaluation_exception. (5) 자연키 upsert로 최근 전환: 근무 경력(2026-09-02, 그룹교체→upsert).</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="40" customHeight="1">
+      <c r="A318" s="24" t="inlineStr">
+        <is>
+          <t>- team_refer.csv는 pipeline/sources.py의 표준 3단계 파이프라인(DRM제거→DB스테이징→후처리) 매니페스트에 속하지 않는다 — process_team_refer.py가 raw_dir(웹 업로드 폴더 또는 data/raw/) 안의 팀참조시트.xlsx/csv를 직접 찾아 읽는 별도 경로이며, 조직 계층(dep_id/upper_dep_id/team_layer) 계산은 pipeline/team_hierarchy.py가 전담한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" s="24" t="inlineStr">
+        <is>
+          <t>- process_project_search.py(과제별 유사 기업/학계 탐색, LLM 파생 산출물)는 process_project_expertise.py와 동일한 Confluence/PDF 문서 요약 캐시를 공유하지만, 딥다이브 분석 로직은 서로 다르다 — project_confl_address.csv를 대상 과제 목록으로 사용할 뿐 원본 인사 데이터 헤더 매핑은 없음(LLM 요약 결과 자체가 산출물).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A317:G317"/>
+    <mergeCell ref="A315:G315"/>
+    <mergeCell ref="A319:G319"/>
+    <mergeCell ref="A318:G318"/>
+    <mergeCell ref="A316:G316"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2911,7 +10330,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="75" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="8" t="n">
         <v>3</v>
       </c>
@@ -2955,10 +10374,57 @@
           <t>"과제 직무/대상자 검증" 화면, JOB Market 근거 A, 메일 리포트</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="J4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>과제별 유사 기업/학계 탐색</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>project_searched_list.csv</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>process_project_search.py</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Confluence/PDF 과제 문서 (project_confl_address.csv 기반, process_project_expertise.py와 동일한 문서 요약 캐시 공유)</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>과제 단위 재분석(문서 캐시 재사용, process_project_expertise.py와 캐시 공유)</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>N (CSV만, JSON_TABLES 미등록)</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>미노출(화이트리스트 없음)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>앱 화면에서 직접 조회하는 곳 없음 — 배치 산출물(CSV)만 생성, 별도 리포트/화면 연동 없음</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1"/>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>※ 이 외에 embedding_cache.json / researcher_pair_judgment.json / journal_authority.json / strength_taxonomy*.json은 화면이 직접 조회하지 않는 순수 캐시·표준화 작업물이라 이 등록부에서 제외했습니다(DB(JSON_TABLES)에도 반영하지 않음).</t>
         </is>
@@ -2973,7 +10439,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
